--- a/BG.xlsx
+++ b/BG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2883D10A-25EB-48D9-B939-26D9B60D57AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A857E17-5C9A-4733-B140-57343964147C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BG!$A$1:$Q$317</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BG!$A$1:$Q$319</definedName>
     <definedName name="Datalist">OFFSET('[1]Data-CPAC'!$A$1,0,0,COUNTA('[1]Data-CPAC'!$A:$A),COUNTA('[1]Data-CPAC'!$1:$1))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="1284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="1285">
   <si>
     <t>วันสิ้นสุด</t>
   </si>
@@ -3893,6 +3893,9 @@
   <si>
     <t>รออนุมัติ</t>
   </si>
+  <si>
+    <t>วงเงินรวมละหานทราย</t>
+  </si>
 </sst>
 </file>
 
@@ -3905,7 +3908,7 @@
     <numFmt numFmtId="166" formatCode="dd/ดดด/yy"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3969,12 +3972,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -4115,334 +4112,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4451,40 +4174,314 @@
     <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="6" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4513,7 +4510,27 @@
     <cellStyle name="Percent 2" xfId="20" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="244">
+  <dxfs count="246">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -14303,7 +14320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47784CE8-ED1A-41FA-99E9-EDA95901941D}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:Q319"/>
@@ -14381,7 +14398,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="2" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A2" s="11" t="s">
         <v>392</v>
       </c>
@@ -14424,7 +14441,7 @@
       <c r="P2" s="15"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:17" ht="17.5" thickBot="1">
+    <row r="3" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A3" s="11" t="s">
         <v>392</v>
       </c>
@@ -14467,7 +14484,7 @@
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
     </row>
-    <row r="4" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="4" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A4" s="16" t="s">
         <v>392</v>
       </c>
@@ -14510,7 +14527,7 @@
       <c r="P4" s="19"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" ht="34.5" thickBot="1">
+    <row r="5" spans="1:17" ht="34.5" hidden="1" thickBot="1">
       <c r="A5" s="52" t="s">
         <v>393</v>
       </c>
@@ -14561,7 +14578,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="17.5" thickBot="1">
+    <row r="6" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A6" s="52" t="s">
         <v>393</v>
       </c>
@@ -14602,7 +14619,7 @@
       <c r="P6" s="60"/>
       <c r="Q6" s="61"/>
     </row>
-    <row r="7" spans="1:17" ht="17.5" thickBot="1">
+    <row r="7" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A7" s="52" t="s">
         <v>393</v>
       </c>
@@ -14643,7 +14660,7 @@
       <c r="P7" s="60"/>
       <c r="Q7" s="61"/>
     </row>
-    <row r="8" spans="1:17" ht="17.5" thickBot="1">
+    <row r="8" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A8" s="52" t="s">
         <v>393</v>
       </c>
@@ -14684,7 +14701,7 @@
       <c r="P8" s="60"/>
       <c r="Q8" s="61"/>
     </row>
-    <row r="9" spans="1:17" ht="17.5" thickBot="1">
+    <row r="9" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A9" s="52" t="s">
         <v>393</v>
       </c>
@@ -14725,7 +14742,7 @@
       <c r="P9" s="60"/>
       <c r="Q9" s="61"/>
     </row>
-    <row r="10" spans="1:17" ht="17.5" thickBot="1">
+    <row r="10" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A10" s="52" t="s">
         <v>393</v>
       </c>
@@ -14766,7 +14783,7 @@
       <c r="P10" s="60"/>
       <c r="Q10" s="61"/>
     </row>
-    <row r="11" spans="1:17" ht="17.5" thickBot="1">
+    <row r="11" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A11" s="52" t="s">
         <v>393</v>
       </c>
@@ -14813,7 +14830,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.5" thickBot="1">
+    <row r="12" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A12" s="52" t="s">
         <v>393</v>
       </c>
@@ -14852,7 +14869,7 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="61"/>
     </row>
-    <row r="13" spans="1:17" ht="17.5" thickBot="1">
+    <row r="13" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A13" s="16" t="s">
         <v>393</v>
       </c>
@@ -14895,7 +14912,7 @@
       <c r="P13" s="19"/>
       <c r="Q13" s="19"/>
     </row>
-    <row r="14" spans="1:17" ht="17.5" thickBot="1">
+    <row r="14" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A14" s="52" t="s">
         <v>393</v>
       </c>
@@ -14942,7 +14959,7 @@
       <c r="P14" s="68"/>
       <c r="Q14" s="68"/>
     </row>
-    <row r="15" spans="1:17" ht="17.5" thickBot="1">
+    <row r="15" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A15" s="52" t="s">
         <v>393</v>
       </c>
@@ -14981,7 +14998,7 @@
       <c r="P15" s="68"/>
       <c r="Q15" s="68"/>
     </row>
-    <row r="16" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="16" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A16" s="52" t="s">
         <v>393</v>
       </c>
@@ -15022,7 +15039,7 @@
       <c r="P16" s="68"/>
       <c r="Q16" s="68"/>
     </row>
-    <row r="17" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="17" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A17" s="52" t="s">
         <v>393</v>
       </c>
@@ -15063,7 +15080,7 @@
       <c r="P17" s="68"/>
       <c r="Q17" s="68"/>
     </row>
-    <row r="18" spans="1:17" ht="17.5" thickBot="1">
+    <row r="18" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A18" s="52" t="s">
         <v>393</v>
       </c>
@@ -15104,7 +15121,7 @@
       <c r="P18" s="60"/>
       <c r="Q18" s="60"/>
     </row>
-    <row r="19" spans="1:17" ht="17.5" thickBot="1">
+    <row r="19" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A19" s="52" t="s">
         <v>393</v>
       </c>
@@ -15147,7 +15164,7 @@
       <c r="P19" s="68"/>
       <c r="Q19" s="68"/>
     </row>
-    <row r="20" spans="1:17" ht="17.5" thickBot="1">
+    <row r="20" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A20" s="11" t="s">
         <v>393</v>
       </c>
@@ -15190,7 +15207,7 @@
       <c r="P20" s="19"/>
       <c r="Q20" s="19"/>
     </row>
-    <row r="21" spans="1:17" ht="17.5" thickBot="1">
+    <row r="21" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A21" s="11" t="s">
         <v>393</v>
       </c>
@@ -15231,7 +15248,7 @@
       <c r="P21" s="15"/>
       <c r="Q21" s="15"/>
     </row>
-    <row r="22" spans="1:17" ht="17.5" thickBot="1">
+    <row r="22" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A22" s="16" t="s">
         <v>393</v>
       </c>
@@ -15274,7 +15291,7 @@
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
     </row>
-    <row r="23" spans="1:17" ht="17.5" thickBot="1">
+    <row r="23" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A23" s="16" t="s">
         <v>393</v>
       </c>
@@ -15317,7 +15334,7 @@
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
     </row>
-    <row r="24" spans="1:17" ht="17.5" thickBot="1">
+    <row r="24" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A24" s="16" t="s">
         <v>393</v>
       </c>
@@ -15360,7 +15377,7 @@
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
     </row>
-    <row r="25" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="25" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A25" s="16" t="s">
         <v>393</v>
       </c>
@@ -15403,7 +15420,7 @@
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
     </row>
-    <row r="26" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="26" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A26" s="16" t="s">
         <v>393</v>
       </c>
@@ -15446,7 +15463,7 @@
       <c r="P26" s="15"/>
       <c r="Q26" s="15"/>
     </row>
-    <row r="27" spans="1:17" ht="17.5" thickBot="1">
+    <row r="27" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A27" s="16" t="s">
         <v>393</v>
       </c>
@@ -15489,7 +15506,7 @@
       <c r="P27" s="19"/>
       <c r="Q27" s="19"/>
     </row>
-    <row r="28" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="28" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A28" s="16" t="s">
         <v>393</v>
       </c>
@@ -15532,7 +15549,7 @@
       <c r="P28" s="15"/>
       <c r="Q28" s="15"/>
     </row>
-    <row r="29" spans="1:17" ht="17.5" thickBot="1">
+    <row r="29" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A29" s="16" t="s">
         <v>393</v>
       </c>
@@ -15575,7 +15592,7 @@
       <c r="P29" s="15"/>
       <c r="Q29" s="15"/>
     </row>
-    <row r="30" spans="1:17" ht="17.5" thickBot="1">
+    <row r="30" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A30" s="16" t="s">
         <v>393</v>
       </c>
@@ -15618,7 +15635,7 @@
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:17" ht="17.5" thickBot="1">
+    <row r="31" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A31" s="52" t="s">
         <v>393</v>
       </c>
@@ -15661,7 +15678,7 @@
       <c r="P31" s="60"/>
       <c r="Q31" s="68"/>
     </row>
-    <row r="32" spans="1:17" ht="17.5" thickBot="1">
+    <row r="32" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A32" s="52" t="s">
         <v>393</v>
       </c>
@@ -15704,7 +15721,7 @@
       <c r="P32" s="60"/>
       <c r="Q32" s="68"/>
     </row>
-    <row r="33" spans="1:17" ht="17.5" thickBot="1">
+    <row r="33" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A33" s="11" t="s">
         <v>393</v>
       </c>
@@ -15747,7 +15764,7 @@
       <c r="P33" s="15"/>
       <c r="Q33" s="15"/>
     </row>
-    <row r="34" spans="1:17" ht="17.5" thickBot="1">
+    <row r="34" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A34" s="16" t="s">
         <v>393</v>
       </c>
@@ -15790,7 +15807,7 @@
       <c r="P34" s="19"/>
       <c r="Q34" s="19"/>
     </row>
-    <row r="35" spans="1:17" ht="17.5" thickBot="1">
+    <row r="35" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A35" s="55" t="s">
         <v>393</v>
       </c>
@@ -15833,7 +15850,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
     </row>
-    <row r="36" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="36" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A36" s="11" t="s">
         <v>393</v>
       </c>
@@ -15876,7 +15893,7 @@
       <c r="P36" s="15"/>
       <c r="Q36" s="20"/>
     </row>
-    <row r="37" spans="1:17" ht="17.5" thickBot="1">
+    <row r="37" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A37" s="11" t="s">
         <v>393</v>
       </c>
@@ -15919,7 +15936,7 @@
       <c r="P37" s="15"/>
       <c r="Q37" s="20"/>
     </row>
-    <row r="38" spans="1:17" ht="17.5" thickBot="1">
+    <row r="38" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A38" s="55" t="s">
         <v>393</v>
       </c>
@@ -15962,7 +15979,7 @@
       <c r="P38" s="60"/>
       <c r="Q38" s="60"/>
     </row>
-    <row r="39" spans="1:17" ht="17.5" thickBot="1">
+    <row r="39" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A39" s="55" t="s">
         <v>393</v>
       </c>
@@ -16013,7 +16030,7 @@
       </c>
       <c r="Q39" s="60"/>
     </row>
-    <row r="40" spans="1:17" ht="17.5" thickBot="1">
+    <row r="40" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A40" s="11" t="s">
         <v>393</v>
       </c>
@@ -16056,7 +16073,7 @@
       <c r="P40" s="15"/>
       <c r="Q40" s="19"/>
     </row>
-    <row r="41" spans="1:17" ht="17.5" thickBot="1">
+    <row r="41" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A41" s="11" t="s">
         <v>393</v>
       </c>
@@ -16097,7 +16114,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="17.5" thickBot="1">
+    <row r="42" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A42" s="16" t="s">
         <v>393</v>
       </c>
@@ -16138,7 +16155,7 @@
       <c r="P42" s="15"/>
       <c r="Q42" s="20"/>
     </row>
-    <row r="43" spans="1:17" ht="17.5" thickBot="1">
+    <row r="43" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A43" s="16" t="s">
         <v>393</v>
       </c>
@@ -16189,7 +16206,7 @@
       </c>
       <c r="Q43" s="19"/>
     </row>
-    <row r="44" spans="1:17" ht="17.5" thickBot="1">
+    <row r="44" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A44" s="16" t="s">
         <v>393</v>
       </c>
@@ -16232,7 +16249,7 @@
       <c r="P44" s="19"/>
       <c r="Q44" s="19"/>
     </row>
-    <row r="45" spans="1:17" ht="17.5" thickBot="1">
+    <row r="45" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A45" s="55" t="s">
         <v>393</v>
       </c>
@@ -16275,7 +16292,7 @@
       <c r="P45" s="60"/>
       <c r="Q45" s="60"/>
     </row>
-    <row r="46" spans="1:17" ht="17.5" thickBot="1">
+    <row r="46" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A46" s="16" t="s">
         <v>393</v>
       </c>
@@ -16316,7 +16333,7 @@
       <c r="P46" s="15"/>
       <c r="Q46" s="15"/>
     </row>
-    <row r="47" spans="1:17" ht="17.5" thickBot="1">
+    <row r="47" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A47" s="16" t="s">
         <v>393</v>
       </c>
@@ -16361,7 +16378,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="17.5" thickBot="1">
+    <row r="48" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A48" s="16" t="s">
         <v>393</v>
       </c>
@@ -16404,7 +16421,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="17.5" thickBot="1">
+    <row r="49" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A49" s="16" t="s">
         <v>824</v>
       </c>
@@ -16447,7 +16464,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="50" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A50" s="16" t="s">
         <v>824</v>
       </c>
@@ -16486,7 +16503,7 @@
       <c r="P50" s="15"/>
       <c r="Q50" s="19"/>
     </row>
-    <row r="51" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="51" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A51" s="16" t="s">
         <v>824</v>
       </c>
@@ -16525,7 +16542,7 @@
       <c r="P51" s="19"/>
       <c r="Q51" s="19"/>
     </row>
-    <row r="52" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="52" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A52" s="16" t="s">
         <v>824</v>
       </c>
@@ -16564,7 +16581,7 @@
       <c r="P52" s="15"/>
       <c r="Q52" s="15"/>
     </row>
-    <row r="53" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="53" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A53" s="11" t="s">
         <v>824</v>
       </c>
@@ -16605,7 +16622,7 @@
       <c r="P53" s="15"/>
       <c r="Q53" s="15"/>
     </row>
-    <row r="54" spans="1:17" ht="17.5" thickBot="1">
+    <row r="54" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A54" s="52" t="s">
         <v>824</v>
       </c>
@@ -16652,7 +16669,7 @@
       <c r="P54" s="74"/>
       <c r="Q54" s="75"/>
     </row>
-    <row r="55" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="55" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A55" s="16" t="s">
         <v>824</v>
       </c>
@@ -16695,7 +16712,7 @@
       <c r="P55" s="19"/>
       <c r="Q55" s="19"/>
     </row>
-    <row r="56" spans="1:17" ht="17.5" thickBot="1">
+    <row r="56" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A56" s="16" t="s">
         <v>824</v>
       </c>
@@ -16736,7 +16753,7 @@
       <c r="P56" s="19"/>
       <c r="Q56" s="19"/>
     </row>
-    <row r="57" spans="1:17" ht="17.5" thickBot="1">
+    <row r="57" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A57" s="16" t="s">
         <v>824</v>
       </c>
@@ -16779,7 +16796,7 @@
       <c r="P57" s="15"/>
       <c r="Q57" s="15"/>
     </row>
-    <row r="58" spans="1:17" ht="17.5" thickBot="1">
+    <row r="58" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A58" s="11" t="s">
         <v>824</v>
       </c>
@@ -16822,7 +16839,7 @@
       <c r="P58" s="15"/>
       <c r="Q58" s="15"/>
     </row>
-    <row r="59" spans="1:17" ht="17.5" thickBot="1">
+    <row r="59" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A59" s="16" t="s">
         <v>824</v>
       </c>
@@ -16865,7 +16882,7 @@
       <c r="P59" s="19"/>
       <c r="Q59" s="19"/>
     </row>
-    <row r="60" spans="1:17" ht="17.5" thickBot="1">
+    <row r="60" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A60" s="16" t="s">
         <v>824</v>
       </c>
@@ -16908,7 +16925,7 @@
       <c r="P60" s="19"/>
       <c r="Q60" s="19"/>
     </row>
-    <row r="61" spans="1:17" ht="17.5" thickBot="1">
+    <row r="61" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A61" s="52" t="s">
         <v>824</v>
       </c>
@@ -16959,7 +16976,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="17.5" thickBot="1">
+    <row r="62" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A62" s="52" t="s">
         <v>824</v>
       </c>
@@ -17000,7 +17017,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="17.5" thickBot="1">
+    <row r="63" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A63" s="52" t="s">
         <v>824</v>
       </c>
@@ -17041,7 +17058,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="17.5" thickBot="1">
+    <row r="64" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A64" s="52" t="s">
         <v>824</v>
       </c>
@@ -17090,7 +17107,7 @@
       </c>
       <c r="Q64" s="68"/>
     </row>
-    <row r="65" spans="1:17" ht="17.5" thickBot="1">
+    <row r="65" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A65" s="52" t="s">
         <v>824</v>
       </c>
@@ -17133,7 +17150,7 @@
       <c r="P65" s="60"/>
       <c r="Q65" s="68"/>
     </row>
-    <row r="66" spans="1:17" ht="17.5" thickBot="1">
+    <row r="66" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A66" s="52" t="s">
         <v>824</v>
       </c>
@@ -17174,7 +17191,7 @@
       <c r="P66" s="68"/>
       <c r="Q66" s="68"/>
     </row>
-    <row r="67" spans="1:17" ht="17.5" thickBot="1">
+    <row r="67" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A67" s="52" t="s">
         <v>824</v>
       </c>
@@ -17217,7 +17234,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="17.5" thickBot="1">
+    <row r="68" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A68" s="52" t="s">
         <v>824</v>
       </c>
@@ -17258,7 +17275,7 @@
       <c r="P68" s="74"/>
       <c r="Q68" s="74"/>
     </row>
-    <row r="69" spans="1:17" ht="17.5" thickBot="1">
+    <row r="69" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A69" s="16" t="s">
         <v>824</v>
       </c>
@@ -17299,7 +17316,7 @@
       <c r="P69" s="19"/>
       <c r="Q69" s="19"/>
     </row>
-    <row r="70" spans="1:17" ht="17.5" thickBot="1">
+    <row r="70" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A70" s="16" t="s">
         <v>397</v>
       </c>
@@ -17340,7 +17357,7 @@
       <c r="P70" s="19"/>
       <c r="Q70" s="19"/>
     </row>
-    <row r="71" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="71" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A71" s="16" t="s">
         <v>397</v>
       </c>
@@ -17381,7 +17398,7 @@
       <c r="P71" s="19"/>
       <c r="Q71" s="19"/>
     </row>
-    <row r="72" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="72" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A72" s="52" t="s">
         <v>397</v>
       </c>
@@ -17422,7 +17439,7 @@
       <c r="P72" s="60"/>
       <c r="Q72" s="60"/>
     </row>
-    <row r="73" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="73" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A73" s="16" t="s">
         <v>397</v>
       </c>
@@ -17465,7 +17482,7 @@
       <c r="P73" s="19"/>
       <c r="Q73" s="19"/>
     </row>
-    <row r="74" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="74" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A74" s="16" t="s">
         <v>397</v>
       </c>
@@ -17508,7 +17525,7 @@
       <c r="P74" s="15"/>
       <c r="Q74" s="15"/>
     </row>
-    <row r="75" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="75" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A75" s="16" t="s">
         <v>397</v>
       </c>
@@ -17549,7 +17566,7 @@
       <c r="P75" s="19"/>
       <c r="Q75" s="19"/>
     </row>
-    <row r="76" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="76" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A76" s="11" t="s">
         <v>397</v>
       </c>
@@ -17592,7 +17609,7 @@
       <c r="P76" s="15"/>
       <c r="Q76" s="15"/>
     </row>
-    <row r="77" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="77" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A77" s="11" t="s">
         <v>397</v>
       </c>
@@ -17637,7 +17654,7 @@
         <v>245366</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="78" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A78" s="11" t="s">
         <v>397</v>
       </c>
@@ -17680,7 +17697,7 @@
       <c r="P78" s="15"/>
       <c r="Q78" s="15"/>
     </row>
-    <row r="79" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="79" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A79" s="11" t="s">
         <v>397</v>
       </c>
@@ -17721,7 +17738,7 @@
       <c r="P79" s="15"/>
       <c r="Q79" s="15"/>
     </row>
-    <row r="80" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="80" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A80" s="11" t="s">
         <v>397</v>
       </c>
@@ -17768,7 +17785,7 @@
       <c r="P80" s="15"/>
       <c r="Q80" s="15"/>
     </row>
-    <row r="81" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="81" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A81" s="11" t="s">
         <v>397</v>
       </c>
@@ -17811,7 +17828,7 @@
       <c r="P81" s="15"/>
       <c r="Q81" s="15"/>
     </row>
-    <row r="82" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="82" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A82" s="11" t="s">
         <v>397</v>
       </c>
@@ -17854,7 +17871,7 @@
       <c r="P82" s="15"/>
       <c r="Q82" s="15"/>
     </row>
-    <row r="83" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="83" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A83" s="16" t="s">
         <v>397</v>
       </c>
@@ -17895,7 +17912,7 @@
       <c r="P83" s="19"/>
       <c r="Q83" s="19"/>
     </row>
-    <row r="84" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="84" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A84" s="16" t="s">
         <v>397</v>
       </c>
@@ -17934,7 +17951,7 @@
       <c r="P84" s="15"/>
       <c r="Q84" s="15"/>
     </row>
-    <row r="85" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="85" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A85" s="16" t="s">
         <v>397</v>
       </c>
@@ -17973,7 +17990,7 @@
       <c r="P85" s="15"/>
       <c r="Q85" s="15"/>
     </row>
-    <row r="86" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="86" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A86" s="16" t="s">
         <v>397</v>
       </c>
@@ -18016,7 +18033,7 @@
       <c r="P86" s="26"/>
       <c r="Q86" s="26"/>
     </row>
-    <row r="87" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="87" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A87" s="16" t="s">
         <v>397</v>
       </c>
@@ -18059,7 +18076,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="88" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A88" s="16" t="s">
         <v>397</v>
       </c>
@@ -18102,7 +18119,7 @@
       <c r="P88" s="19"/>
       <c r="Q88" s="19"/>
     </row>
-    <row r="89" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="89" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A89" s="11" t="s">
         <v>397</v>
       </c>
@@ -18149,7 +18166,7 @@
       <c r="P89" s="15"/>
       <c r="Q89" s="15"/>
     </row>
-    <row r="90" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="90" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A90" s="11" t="s">
         <v>397</v>
       </c>
@@ -18192,7 +18209,7 @@
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
     </row>
-    <row r="91" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="91" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A91" s="11" t="s">
         <v>397</v>
       </c>
@@ -18235,7 +18252,7 @@
       <c r="P91" s="15"/>
       <c r="Q91" s="15"/>
     </row>
-    <row r="92" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="92" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A92" s="11" t="s">
         <v>397</v>
       </c>
@@ -18278,7 +18295,7 @@
       <c r="P92" s="15"/>
       <c r="Q92" s="15"/>
     </row>
-    <row r="93" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="93" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A93" s="11" t="s">
         <v>397</v>
       </c>
@@ -18321,7 +18338,7 @@
       <c r="P93" s="15"/>
       <c r="Q93" s="15"/>
     </row>
-    <row r="94" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="94" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A94" s="11" t="s">
         <v>397</v>
       </c>
@@ -18364,7 +18381,7 @@
       <c r="P94" s="15"/>
       <c r="Q94" s="15"/>
     </row>
-    <row r="95" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="95" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A95" s="11" t="s">
         <v>397</v>
       </c>
@@ -18407,7 +18424,7 @@
       <c r="P95" s="15"/>
       <c r="Q95" s="15"/>
     </row>
-    <row r="96" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="96" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A96" s="11" t="s">
         <v>397</v>
       </c>
@@ -18450,7 +18467,7 @@
       <c r="P96" s="26"/>
       <c r="Q96" s="26"/>
     </row>
-    <row r="97" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="97" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A97" s="11" t="s">
         <v>397</v>
       </c>
@@ -18493,7 +18510,7 @@
       <c r="P97" s="15"/>
       <c r="Q97" s="15"/>
     </row>
-    <row r="98" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="98" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A98" s="11" t="s">
         <v>397</v>
       </c>
@@ -18536,7 +18553,7 @@
       <c r="P98" s="15"/>
       <c r="Q98" s="15"/>
     </row>
-    <row r="99" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="99" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A99" s="11" t="s">
         <v>397</v>
       </c>
@@ -18579,7 +18596,7 @@
       <c r="P99" s="15"/>
       <c r="Q99" s="15"/>
     </row>
-    <row r="100" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="100" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A100" s="11" t="s">
         <v>397</v>
       </c>
@@ -18620,7 +18637,7 @@
       <c r="P100" s="20"/>
       <c r="Q100" s="20"/>
     </row>
-    <row r="101" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="101" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A101" s="16" t="s">
         <v>397</v>
       </c>
@@ -18661,7 +18678,7 @@
       <c r="P101" s="19"/>
       <c r="Q101" s="19"/>
     </row>
-    <row r="102" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="102" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A102" s="16" t="s">
         <v>397</v>
       </c>
@@ -18702,7 +18719,7 @@
       <c r="P102" s="19"/>
       <c r="Q102" s="19"/>
     </row>
-    <row r="103" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="103" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A103" s="52" t="s">
         <v>397</v>
       </c>
@@ -18743,7 +18760,7 @@
       <c r="P103" s="68"/>
       <c r="Q103" s="61"/>
     </row>
-    <row r="104" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="104" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A104" s="55" t="s">
         <v>397</v>
       </c>
@@ -18786,7 +18803,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="105" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A105" s="11" t="s">
         <v>397</v>
       </c>
@@ -18827,7 +18844,7 @@
       <c r="P105" s="15"/>
       <c r="Q105" s="15"/>
     </row>
-    <row r="106" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="106" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A106" s="11" t="s">
         <v>397</v>
       </c>
@@ -18870,7 +18887,7 @@
       <c r="P106" s="15"/>
       <c r="Q106" s="15"/>
     </row>
-    <row r="107" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="107" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A107" s="11" t="s">
         <v>397</v>
       </c>
@@ -18913,7 +18930,7 @@
       <c r="P107" s="15"/>
       <c r="Q107" s="15"/>
     </row>
-    <row r="108" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="108" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A108" s="11" t="s">
         <v>397</v>
       </c>
@@ -18955,7 +18972,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="109" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A109" s="16" t="s">
         <v>397</v>
       </c>
@@ -19004,7 +19021,7 @@
       <c r="P109" s="19"/>
       <c r="Q109" s="19"/>
     </row>
-    <row r="110" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="110" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A110" s="16" t="s">
         <v>397</v>
       </c>
@@ -19055,7 +19072,7 @@
       </c>
       <c r="Q110" s="19"/>
     </row>
-    <row r="111" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="111" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A111" s="16" t="s">
         <v>397</v>
       </c>
@@ -19096,7 +19113,7 @@
       <c r="P111" s="19"/>
       <c r="Q111" s="19"/>
     </row>
-    <row r="112" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="112" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A112" s="16" t="s">
         <v>397</v>
       </c>
@@ -19135,7 +19152,7 @@
       <c r="P112" s="19"/>
       <c r="Q112" s="19"/>
     </row>
-    <row r="113" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="113" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A113" s="16" t="s">
         <v>397</v>
       </c>
@@ -19174,7 +19191,7 @@
       <c r="P113" s="19"/>
       <c r="Q113" s="19"/>
     </row>
-    <row r="114" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="114" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A114" s="16" t="s">
         <v>397</v>
       </c>
@@ -19213,7 +19230,7 @@
       <c r="P114" s="15"/>
       <c r="Q114" s="19"/>
     </row>
-    <row r="115" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="115" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A115" s="16" t="s">
         <v>397</v>
       </c>
@@ -19252,7 +19269,7 @@
       <c r="P115" s="15"/>
       <c r="Q115" s="19"/>
     </row>
-    <row r="116" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="116" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A116" s="16" t="s">
         <v>397</v>
       </c>
@@ -19295,7 +19312,7 @@
       <c r="P116" s="19"/>
       <c r="Q116" s="19"/>
     </row>
-    <row r="117" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="117" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A117" s="16" t="s">
         <v>397</v>
       </c>
@@ -19336,7 +19353,7 @@
       <c r="P117" s="19"/>
       <c r="Q117" s="19"/>
     </row>
-    <row r="118" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="118" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A118" s="16" t="s">
         <v>397</v>
       </c>
@@ -19377,7 +19394,7 @@
       <c r="P118" s="19"/>
       <c r="Q118" s="19"/>
     </row>
-    <row r="119" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="119" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A119" s="16" t="s">
         <v>397</v>
       </c>
@@ -19418,7 +19435,7 @@
       <c r="P119" s="19"/>
       <c r="Q119" s="19"/>
     </row>
-    <row r="120" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="120" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A120" s="16" t="s">
         <v>397</v>
       </c>
@@ -19459,7 +19476,7 @@
       <c r="P120" s="19"/>
       <c r="Q120" s="19"/>
     </row>
-    <row r="121" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="121" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A121" s="16" t="s">
         <v>397</v>
       </c>
@@ -19506,7 +19523,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="122" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A122" s="16" t="s">
         <v>397</v>
       </c>
@@ -19551,7 +19568,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="123" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A123" s="16" t="s">
         <v>397</v>
       </c>
@@ -19592,7 +19609,7 @@
       <c r="P123" s="19"/>
       <c r="Q123" s="34"/>
     </row>
-    <row r="124" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="124" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A124" s="16" t="s">
         <v>397</v>
       </c>
@@ -19631,7 +19648,7 @@
       <c r="P124" s="19"/>
       <c r="Q124" s="34"/>
     </row>
-    <row r="125" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="125" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A125" s="16" t="s">
         <v>397</v>
       </c>
@@ -19670,7 +19687,7 @@
       <c r="P125" s="15"/>
       <c r="Q125" s="15"/>
     </row>
-    <row r="126" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="126" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A126" s="11" t="s">
         <v>397</v>
       </c>
@@ -19711,7 +19728,7 @@
       <c r="P126" s="15"/>
       <c r="Q126" s="19"/>
     </row>
-    <row r="127" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="127" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A127" s="11" t="s">
         <v>397</v>
       </c>
@@ -19750,7 +19767,7 @@
       <c r="P127" s="15"/>
       <c r="Q127" s="15"/>
     </row>
-    <row r="128" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="128" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A128" s="11" t="s">
         <v>397</v>
       </c>
@@ -19789,7 +19806,7 @@
       <c r="P128" s="15"/>
       <c r="Q128" s="15"/>
     </row>
-    <row r="129" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="129" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A129" s="11" t="s">
         <v>397</v>
       </c>
@@ -19832,7 +19849,7 @@
       <c r="P129" s="15"/>
       <c r="Q129" s="15"/>
     </row>
-    <row r="130" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="130" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A130" s="52" t="s">
         <v>397</v>
       </c>
@@ -19873,7 +19890,7 @@
       <c r="P130" s="60"/>
       <c r="Q130" s="61"/>
     </row>
-    <row r="131" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="131" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A131" s="52" t="s">
         <v>397</v>
       </c>
@@ -19926,7 +19943,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="132" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A132" s="52" t="s">
         <v>397</v>
       </c>
@@ -19967,7 +19984,7 @@
       <c r="P132" s="60"/>
       <c r="Q132" s="60"/>
     </row>
-    <row r="133" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="133" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A133" s="52" t="s">
         <v>397</v>
       </c>
@@ -20008,7 +20025,7 @@
       <c r="P133" s="60"/>
       <c r="Q133" s="60"/>
     </row>
-    <row r="134" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="134" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A134" s="16" t="s">
         <v>397</v>
       </c>
@@ -20049,7 +20066,7 @@
       <c r="P134" s="15"/>
       <c r="Q134" s="15"/>
     </row>
-    <row r="135" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="135" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A135" s="52" t="s">
         <v>397</v>
       </c>
@@ -20090,7 +20107,7 @@
       <c r="P135" s="68"/>
       <c r="Q135" s="68"/>
     </row>
-    <row r="136" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="136" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A136" s="52" t="s">
         <v>397</v>
       </c>
@@ -20129,7 +20146,7 @@
       <c r="P136" s="68"/>
       <c r="Q136" s="68"/>
     </row>
-    <row r="137" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="137" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A137" s="52" t="s">
         <v>397</v>
       </c>
@@ -20168,7 +20185,7 @@
       <c r="P137" s="68"/>
       <c r="Q137" s="68"/>
     </row>
-    <row r="138" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="138" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A138" s="52" t="s">
         <v>397</v>
       </c>
@@ -20211,7 +20228,7 @@
       <c r="P138" s="68"/>
       <c r="Q138" s="68"/>
     </row>
-    <row r="139" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="139" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A139" s="16" t="s">
         <v>397</v>
       </c>
@@ -20254,7 +20271,7 @@
       <c r="P139" s="26"/>
       <c r="Q139" s="26"/>
     </row>
-    <row r="140" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="140" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A140" s="16" t="s">
         <v>397</v>
       </c>
@@ -20297,7 +20314,7 @@
       <c r="P140" s="26"/>
       <c r="Q140" s="26"/>
     </row>
-    <row r="141" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="141" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A141" s="16" t="s">
         <v>397</v>
       </c>
@@ -20340,7 +20357,7 @@
       <c r="P141" s="15"/>
       <c r="Q141" s="15"/>
     </row>
-    <row r="142" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="142" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A142" s="16" t="s">
         <v>397</v>
       </c>
@@ -20381,7 +20398,7 @@
       <c r="P142" s="19"/>
       <c r="Q142" s="19"/>
     </row>
-    <row r="143" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="143" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A143" s="16" t="s">
         <v>397</v>
       </c>
@@ -20420,7 +20437,7 @@
       <c r="P143" s="19"/>
       <c r="Q143" s="19"/>
     </row>
-    <row r="144" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="144" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A144" s="16" t="s">
         <v>397</v>
       </c>
@@ -20461,7 +20478,7 @@
       <c r="P144" s="15"/>
       <c r="Q144" s="15"/>
     </row>
-    <row r="145" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="145" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A145" s="11" t="s">
         <v>397</v>
       </c>
@@ -20504,7 +20521,7 @@
       <c r="P145" s="15"/>
       <c r="Q145" s="15"/>
     </row>
-    <row r="146" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="146" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A146" s="11" t="s">
         <v>397</v>
       </c>
@@ -20545,7 +20562,7 @@
       <c r="P146" s="15"/>
       <c r="Q146" s="15"/>
     </row>
-    <row r="147" spans="1:17" ht="17.5" thickBot="1">
+    <row r="147" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A147" s="16" t="s">
         <v>399</v>
       </c>
@@ -20588,7 +20605,7 @@
       <c r="P147" s="35"/>
       <c r="Q147" s="35"/>
     </row>
-    <row r="148" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="148" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A148" s="16" t="s">
         <v>399</v>
       </c>
@@ -20631,7 +20648,7 @@
       <c r="P148" s="19"/>
       <c r="Q148" s="19"/>
     </row>
-    <row r="149" spans="1:17" ht="17.5" thickBot="1">
+    <row r="149" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A149" s="16" t="s">
         <v>399</v>
       </c>
@@ -20674,7 +20691,7 @@
       <c r="P149" s="19"/>
       <c r="Q149" s="19"/>
     </row>
-    <row r="150" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="150" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A150" s="16" t="s">
         <v>399</v>
       </c>
@@ -20717,7 +20734,7 @@
       <c r="P150" s="19"/>
       <c r="Q150" s="19"/>
     </row>
-    <row r="151" spans="1:17" ht="17.5" thickBot="1">
+    <row r="151" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A151" s="16" t="s">
         <v>399</v>
       </c>
@@ -20760,7 +20777,7 @@
       <c r="P151" s="19"/>
       <c r="Q151" s="19"/>
     </row>
-    <row r="152" spans="1:17" ht="17.5" thickBot="1">
+    <row r="152" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A152" s="16" t="s">
         <v>399</v>
       </c>
@@ -20803,7 +20820,7 @@
       <c r="P152" s="15"/>
       <c r="Q152" s="15"/>
     </row>
-    <row r="153" spans="1:17" ht="17.5" thickBot="1">
+    <row r="153" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A153" s="11" t="s">
         <v>399</v>
       </c>
@@ -20846,7 +20863,7 @@
       <c r="P153" s="15"/>
       <c r="Q153" s="15"/>
     </row>
-    <row r="154" spans="1:17" ht="17.5" thickBot="1">
+    <row r="154" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A154" s="11" t="s">
         <v>399</v>
       </c>
@@ -20889,7 +20906,7 @@
       <c r="P154" s="15"/>
       <c r="Q154" s="15"/>
     </row>
-    <row r="155" spans="1:17" ht="17.5" thickBot="1">
+    <row r="155" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A155" s="16" t="s">
         <v>399</v>
       </c>
@@ -20932,7 +20949,7 @@
       <c r="P155" s="15"/>
       <c r="Q155" s="15"/>
     </row>
-    <row r="156" spans="1:17" ht="17.5" thickBot="1">
+    <row r="156" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A156" s="16" t="s">
         <v>399</v>
       </c>
@@ -20975,7 +20992,7 @@
       <c r="P156" s="15"/>
       <c r="Q156" s="15"/>
     </row>
-    <row r="157" spans="1:17" ht="17.5" thickBot="1">
+    <row r="157" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A157" s="11" t="s">
         <v>399</v>
       </c>
@@ -21018,7 +21035,7 @@
       <c r="P157" s="15"/>
       <c r="Q157" s="15"/>
     </row>
-    <row r="158" spans="1:17" ht="17.5" thickBot="1">
+    <row r="158" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A158" s="16" t="s">
         <v>399</v>
       </c>
@@ -21061,7 +21078,7 @@
       <c r="P158" s="15"/>
       <c r="Q158" s="15"/>
     </row>
-    <row r="159" spans="1:17" ht="17.5" thickBot="1">
+    <row r="159" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A159" s="16" t="s">
         <v>399</v>
       </c>
@@ -21104,7 +21121,7 @@
       <c r="P159" s="15"/>
       <c r="Q159" s="15"/>
     </row>
-    <row r="160" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="160" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A160" s="16" t="s">
         <v>399</v>
       </c>
@@ -21147,7 +21164,7 @@
       <c r="P160" s="19"/>
       <c r="Q160" s="19"/>
     </row>
-    <row r="161" spans="1:17" ht="17.5" thickBot="1">
+    <row r="161" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A161" s="16" t="s">
         <v>399</v>
       </c>
@@ -21190,7 +21207,7 @@
       <c r="P161" s="15"/>
       <c r="Q161" s="15"/>
     </row>
-    <row r="162" spans="1:17" ht="17.5" thickBot="1">
+    <row r="162" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A162" s="16" t="s">
         <v>399</v>
       </c>
@@ -21233,7 +21250,7 @@
       <c r="P162" s="19"/>
       <c r="Q162" s="19"/>
     </row>
-    <row r="163" spans="1:17" ht="17.5" thickBot="1">
+    <row r="163" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A163" s="55" t="s">
         <v>399</v>
       </c>
@@ -21276,7 +21293,7 @@
       <c r="P163" s="60"/>
       <c r="Q163" s="60"/>
     </row>
-    <row r="164" spans="1:17" ht="17.5" thickBot="1">
+    <row r="164" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A164" s="55" t="s">
         <v>399</v>
       </c>
@@ -21317,7 +21334,7 @@
       <c r="P164" s="60"/>
       <c r="Q164" s="60"/>
     </row>
-    <row r="165" spans="1:17" ht="17.5" thickBot="1">
+    <row r="165" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A165" s="55" t="s">
         <v>399</v>
       </c>
@@ -21358,7 +21375,7 @@
       <c r="P165" s="60"/>
       <c r="Q165" s="60"/>
     </row>
-    <row r="166" spans="1:17" ht="17.5" thickBot="1">
+    <row r="166" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A166" s="11" t="s">
         <v>399</v>
       </c>
@@ -21409,7 +21426,7 @@
       </c>
       <c r="Q166" s="36"/>
     </row>
-    <row r="167" spans="1:17" ht="17.5" thickBot="1">
+    <row r="167" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A167" s="55" t="s">
         <v>399</v>
       </c>
@@ -21462,7 +21479,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="168" spans="1:17" ht="17.5" thickBot="1">
+    <row r="168" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A168" s="52" t="s">
         <v>399</v>
       </c>
@@ -21503,7 +21520,7 @@
       <c r="P168" s="87"/>
       <c r="Q168" s="87"/>
     </row>
-    <row r="169" spans="1:17" ht="17.5" thickBot="1">
+    <row r="169" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A169" s="52" t="s">
         <v>399</v>
       </c>
@@ -21546,7 +21563,7 @@
       <c r="P169" s="60"/>
       <c r="Q169" s="60"/>
     </row>
-    <row r="170" spans="1:17" ht="17.5" thickBot="1">
+    <row r="170" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A170" s="16" t="s">
         <v>399</v>
       </c>
@@ -21589,7 +21606,7 @@
       <c r="P170" s="35"/>
       <c r="Q170" s="35"/>
     </row>
-    <row r="171" spans="1:17" ht="17.5" thickBot="1">
+    <row r="171" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A171" s="16" t="s">
         <v>399</v>
       </c>
@@ -21630,7 +21647,7 @@
       <c r="P171" s="35"/>
       <c r="Q171" s="35"/>
     </row>
-    <row r="172" spans="1:17" ht="17.5" thickBot="1">
+    <row r="172" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A172" s="11" t="s">
         <v>399</v>
       </c>
@@ -21673,7 +21690,7 @@
       <c r="P172" s="26"/>
       <c r="Q172" s="26"/>
     </row>
-    <row r="173" spans="1:17" ht="17.5" thickBot="1">
+    <row r="173" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A173" s="11" t="s">
         <v>399</v>
       </c>
@@ -21724,7 +21741,7 @@
       </c>
       <c r="Q173" s="15"/>
     </row>
-    <row r="174" spans="1:17" ht="17.5" thickBot="1">
+    <row r="174" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A174" s="11" t="s">
         <v>399</v>
       </c>
@@ -21767,7 +21784,7 @@
       <c r="P174" s="15"/>
       <c r="Q174" s="15"/>
     </row>
-    <row r="175" spans="1:17" ht="17.5" thickBot="1">
+    <row r="175" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A175" s="55" t="s">
         <v>399</v>
       </c>
@@ -21816,7 +21833,7 @@
       <c r="P175" s="88"/>
       <c r="Q175" s="88"/>
     </row>
-    <row r="176" spans="1:17" ht="17.5" thickBot="1">
+    <row r="176" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A176" s="11" t="s">
         <v>399</v>
       </c>
@@ -21859,7 +21876,7 @@
       <c r="P176" s="20"/>
       <c r="Q176" s="20"/>
     </row>
-    <row r="177" spans="1:17" ht="17.5" thickBot="1">
+    <row r="177" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A177" s="11" t="s">
         <v>399</v>
       </c>
@@ -21902,7 +21919,7 @@
       <c r="P177" s="15"/>
       <c r="Q177" s="15"/>
     </row>
-    <row r="178" spans="1:17" ht="17.5" thickBot="1">
+    <row r="178" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A178" s="11" t="s">
         <v>399</v>
       </c>
@@ -21945,7 +21962,7 @@
       <c r="P178" s="15"/>
       <c r="Q178" s="15"/>
     </row>
-    <row r="179" spans="1:17" ht="17.5" thickBot="1">
+    <row r="179" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A179" s="52" t="s">
         <v>399</v>
       </c>
@@ -21988,7 +22005,7 @@
       <c r="P179" s="60"/>
       <c r="Q179" s="60"/>
     </row>
-    <row r="180" spans="1:17" ht="17.5" thickBot="1">
+    <row r="180" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A180" s="55" t="s">
         <v>399</v>
       </c>
@@ -22029,7 +22046,7 @@
       <c r="P180" s="60"/>
       <c r="Q180" s="60"/>
     </row>
-    <row r="181" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="181" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A181" s="52" t="s">
         <v>399</v>
       </c>
@@ -22070,7 +22087,7 @@
       <c r="P181" s="60"/>
       <c r="Q181" s="60"/>
     </row>
-    <row r="182" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="182" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A182" s="55" t="s">
         <v>399</v>
       </c>
@@ -22123,7 +22140,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="183" spans="1:17" ht="17.5" thickBot="1">
+    <row r="183" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A183" s="55" t="s">
         <v>399</v>
       </c>
@@ -22164,7 +22181,7 @@
       <c r="P183" s="60"/>
       <c r="Q183" s="60"/>
     </row>
-    <row r="184" spans="1:17" ht="17.5" thickBot="1">
+    <row r="184" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A184" s="55" t="s">
         <v>399</v>
       </c>
@@ -22205,7 +22222,7 @@
       <c r="P184" s="60"/>
       <c r="Q184" s="60"/>
     </row>
-    <row r="185" spans="1:17" ht="17.5" thickBot="1">
+    <row r="185" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A185" s="52" t="s">
         <v>399</v>
       </c>
@@ -22248,7 +22265,7 @@
       <c r="P185" s="88"/>
       <c r="Q185" s="88"/>
     </row>
-    <row r="186" spans="1:17" ht="17.5" thickBot="1">
+    <row r="186" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A186" s="52" t="s">
         <v>399</v>
       </c>
@@ -22291,7 +22308,7 @@
       <c r="P186" s="88"/>
       <c r="Q186" s="88"/>
     </row>
-    <row r="187" spans="1:17" ht="17.5" thickBot="1">
+    <row r="187" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A187" s="16" t="s">
         <v>399</v>
       </c>
@@ -22334,7 +22351,7 @@
       <c r="P187" s="26"/>
       <c r="Q187" s="26"/>
     </row>
-    <row r="188" spans="1:17" ht="17.5" thickBot="1">
+    <row r="188" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A188" s="11" t="s">
         <v>399</v>
       </c>
@@ -22377,7 +22394,7 @@
       <c r="P188" s="19"/>
       <c r="Q188" s="19"/>
     </row>
-    <row r="189" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="189" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A189" s="11" t="s">
         <v>399</v>
       </c>
@@ -22420,7 +22437,7 @@
       <c r="P189" s="15"/>
       <c r="Q189" s="15"/>
     </row>
-    <row r="190" spans="1:17" ht="17.5" thickBot="1">
+    <row r="190" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A190" s="11" t="s">
         <v>399</v>
       </c>
@@ -22463,7 +22480,7 @@
       <c r="P190" s="15"/>
       <c r="Q190" s="15"/>
     </row>
-    <row r="191" spans="1:17" ht="17.5" thickBot="1">
+    <row r="191" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A191" s="16" t="s">
         <v>399</v>
       </c>
@@ -22504,7 +22521,7 @@
       <c r="P191" s="15"/>
       <c r="Q191" s="15"/>
     </row>
-    <row r="192" spans="1:17" ht="17.5" thickBot="1">
+    <row r="192" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A192" s="11" t="s">
         <v>399</v>
       </c>
@@ -22547,7 +22564,7 @@
       <c r="P192" s="43"/>
       <c r="Q192" s="43"/>
     </row>
-    <row r="193" spans="1:17" ht="17.5" thickBot="1">
+    <row r="193" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A193" s="11" t="s">
         <v>399</v>
       </c>
@@ -22590,7 +22607,7 @@
       <c r="P193" s="15"/>
       <c r="Q193" s="15"/>
     </row>
-    <row r="194" spans="1:17" ht="17.5" thickBot="1">
+    <row r="194" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A194" s="55" t="s">
         <v>399</v>
       </c>
@@ -22633,7 +22650,7 @@
       <c r="P194" s="60"/>
       <c r="Q194" s="60"/>
     </row>
-    <row r="195" spans="1:17" ht="17.5" thickBot="1">
+    <row r="195" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A195" s="55" t="s">
         <v>399</v>
       </c>
@@ -22676,7 +22693,7 @@
       <c r="P195" s="60"/>
       <c r="Q195" s="60"/>
     </row>
-    <row r="196" spans="1:17" ht="17.5" thickBot="1">
+    <row r="196" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A196" s="55" t="s">
         <v>399</v>
       </c>
@@ -22719,7 +22736,7 @@
       <c r="P196" s="60"/>
       <c r="Q196" s="60"/>
     </row>
-    <row r="197" spans="1:17" ht="17.5" thickBot="1">
+    <row r="197" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A197" s="16" t="s">
         <v>399</v>
       </c>
@@ -22762,7 +22779,7 @@
       <c r="P197" s="19"/>
       <c r="Q197" s="19"/>
     </row>
-    <row r="198" spans="1:17" ht="17.5" thickBot="1">
+    <row r="198" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A198" s="16" t="s">
         <v>399</v>
       </c>
@@ -22805,7 +22822,7 @@
       <c r="P198" s="19"/>
       <c r="Q198" s="19"/>
     </row>
-    <row r="199" spans="1:17" ht="17.5" thickBot="1">
+    <row r="199" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A199" s="16" t="s">
         <v>399</v>
       </c>
@@ -22848,7 +22865,7 @@
       <c r="P199" s="19"/>
       <c r="Q199" s="19"/>
     </row>
-    <row r="200" spans="1:17" ht="17.5" thickBot="1">
+    <row r="200" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A200" s="16" t="s">
         <v>399</v>
       </c>
@@ -22891,7 +22908,7 @@
       <c r="P200" s="19"/>
       <c r="Q200" s="19"/>
     </row>
-    <row r="201" spans="1:17" ht="17.5" thickBot="1">
+    <row r="201" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A201" s="16" t="s">
         <v>399</v>
       </c>
@@ -22934,7 +22951,7 @@
       <c r="P201" s="15"/>
       <c r="Q201" s="15"/>
     </row>
-    <row r="202" spans="1:17" ht="17.5" thickBot="1">
+    <row r="202" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A202" s="16" t="s">
         <v>399</v>
       </c>
@@ -22977,7 +22994,7 @@
       <c r="P202" s="15"/>
       <c r="Q202" s="15"/>
     </row>
-    <row r="203" spans="1:17" ht="17.5" thickBot="1">
+    <row r="203" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A203" s="16" t="s">
         <v>399</v>
       </c>
@@ -23020,7 +23037,7 @@
       <c r="P203" s="15"/>
       <c r="Q203" s="15"/>
     </row>
-    <row r="204" spans="1:17" ht="17.5" thickBot="1">
+    <row r="204" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A204" s="16" t="s">
         <v>399</v>
       </c>
@@ -23063,7 +23080,7 @@
       <c r="P204" s="15"/>
       <c r="Q204" s="15"/>
     </row>
-    <row r="205" spans="1:17" ht="17.5" thickBot="1">
+    <row r="205" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A205" s="16" t="s">
         <v>399</v>
       </c>
@@ -23106,7 +23123,7 @@
       <c r="P205" s="15"/>
       <c r="Q205" s="15"/>
     </row>
-    <row r="206" spans="1:17" ht="17.5" thickBot="1">
+    <row r="206" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A206" s="16" t="s">
         <v>399</v>
       </c>
@@ -23149,7 +23166,7 @@
       <c r="P206" s="19"/>
       <c r="Q206" s="19"/>
     </row>
-    <row r="207" spans="1:17" ht="17.5" thickBot="1">
+    <row r="207" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A207" s="16" t="s">
         <v>399</v>
       </c>
@@ -23192,7 +23209,7 @@
       <c r="P207" s="19"/>
       <c r="Q207" s="19"/>
     </row>
-    <row r="208" spans="1:17" ht="17.5" thickBot="1">
+    <row r="208" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A208" s="16" t="s">
         <v>399</v>
       </c>
@@ -23235,7 +23252,7 @@
       <c r="P208" s="19"/>
       <c r="Q208" s="19"/>
     </row>
-    <row r="209" spans="1:17" ht="17.5" thickBot="1">
+    <row r="209" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A209" s="55" t="s">
         <v>399</v>
       </c>
@@ -23286,7 +23303,7 @@
       </c>
       <c r="Q209" s="60"/>
     </row>
-    <row r="210" spans="1:17" ht="17.5" thickBot="1">
+    <row r="210" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A210" s="11" t="s">
         <v>399</v>
       </c>
@@ -23358,17 +23375,13 @@
         <v>2</v>
       </c>
       <c r="J211" s="13">
-        <v>244590</v>
+        <v>244955</v>
       </c>
       <c r="K211" s="24">
         <v>500000</v>
       </c>
-      <c r="L211" s="24">
-        <v>1000000</v>
-      </c>
-      <c r="M211" s="70" t="s">
-        <v>1256</v>
-      </c>
+      <c r="L211" s="24"/>
+      <c r="M211" s="70"/>
       <c r="N211" s="13" t="s">
         <v>899</v>
       </c>
@@ -23411,9 +23424,11 @@
         <v>2</v>
       </c>
       <c r="J212" s="13">
-        <v>244590</v>
-      </c>
-      <c r="K212" s="24"/>
+        <v>244955</v>
+      </c>
+      <c r="K212" s="24" t="s">
+        <v>1284</v>
+      </c>
       <c r="L212" s="24"/>
       <c r="M212" s="70"/>
       <c r="N212" s="13" t="s">
@@ -23423,7 +23438,7 @@
       <c r="P212" s="15"/>
       <c r="Q212" s="15"/>
     </row>
-    <row r="213" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="213" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A213" s="11" t="s">
         <v>399</v>
       </c>
@@ -23466,7 +23481,7 @@
       <c r="P213" s="15"/>
       <c r="Q213" s="15"/>
     </row>
-    <row r="214" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="214" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A214" s="11" t="s">
         <v>399</v>
       </c>
@@ -23509,7 +23524,7 @@
       <c r="P214" s="15"/>
       <c r="Q214" s="15"/>
     </row>
-    <row r="215" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="215" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A215" s="11" t="s">
         <v>399</v>
       </c>
@@ -23552,7 +23567,7 @@
       <c r="P215" s="15"/>
       <c r="Q215" s="15"/>
     </row>
-    <row r="216" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="216" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A216" s="11" t="s">
         <v>399</v>
       </c>
@@ -23595,7 +23610,7 @@
       <c r="P216" s="15"/>
       <c r="Q216" s="15"/>
     </row>
-    <row r="217" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="217" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A217" s="11" t="s">
         <v>399</v>
       </c>
@@ -23638,7 +23653,7 @@
       <c r="P217" s="15"/>
       <c r="Q217" s="15"/>
     </row>
-    <row r="218" spans="1:17" ht="34.5" thickBot="1">
+    <row r="218" spans="1:17" ht="34.5" hidden="1" thickBot="1">
       <c r="A218" s="11" t="s">
         <v>399</v>
       </c>
@@ -23683,7 +23698,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="219" spans="1:17" ht="17.5" thickBot="1">
+    <row r="219" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A219" s="11" t="s">
         <v>399</v>
       </c>
@@ -23724,7 +23739,7 @@
       <c r="P219" s="15"/>
       <c r="Q219" s="26"/>
     </row>
-    <row r="220" spans="1:17" ht="17.5" thickBot="1">
+    <row r="220" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A220" s="16" t="s">
         <v>399</v>
       </c>
@@ -23775,7 +23790,7 @@
       </c>
       <c r="Q220" s="19"/>
     </row>
-    <row r="221" spans="1:17" ht="17.5" thickBot="1">
+    <row r="221" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A221" s="16" t="s">
         <v>399</v>
       </c>
@@ -23826,7 +23841,7 @@
       </c>
       <c r="Q221" s="15"/>
     </row>
-    <row r="222" spans="1:17" ht="17.5" thickBot="1">
+    <row r="222" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A222" s="52" t="s">
         <v>399</v>
       </c>
@@ -23877,7 +23892,7 @@
       </c>
       <c r="Q222" s="60"/>
     </row>
-    <row r="223" spans="1:17" ht="17.5" thickBot="1">
+    <row r="223" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A223" s="16" t="s">
         <v>399</v>
       </c>
@@ -23918,7 +23933,7 @@
       <c r="P223" s="15"/>
       <c r="Q223" s="15"/>
     </row>
-    <row r="224" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="224" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A224" s="11" t="s">
         <v>399</v>
       </c>
@@ -23959,7 +23974,7 @@
       <c r="P224" s="15"/>
       <c r="Q224" s="15"/>
     </row>
-    <row r="225" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="225" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A225" s="11" t="s">
         <v>399</v>
       </c>
@@ -24002,7 +24017,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="226" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="226" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A226" s="11" t="s">
         <v>399</v>
       </c>
@@ -24043,7 +24058,7 @@
       <c r="P226" s="15"/>
       <c r="Q226" s="15"/>
     </row>
-    <row r="227" spans="1:17" ht="17.5" thickBot="1">
+    <row r="227" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A227" s="11" t="s">
         <v>399</v>
       </c>
@@ -24086,7 +24101,7 @@
       <c r="P227" s="19"/>
       <c r="Q227" s="19"/>
     </row>
-    <row r="228" spans="1:17" ht="17.5" thickBot="1">
+    <row r="228" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A228" s="11" t="s">
         <v>399</v>
       </c>
@@ -24127,7 +24142,7 @@
       <c r="P228" s="15"/>
       <c r="Q228" s="15"/>
     </row>
-    <row r="229" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="229" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A229" s="11" t="s">
         <v>399</v>
       </c>
@@ -24170,7 +24185,7 @@
       <c r="P229" s="15"/>
       <c r="Q229" s="15"/>
     </row>
-    <row r="230" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="230" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A230" s="16" t="s">
         <v>399</v>
       </c>
@@ -24211,7 +24226,7 @@
       <c r="P230" s="15"/>
       <c r="Q230" s="15"/>
     </row>
-    <row r="231" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="231" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A231" s="16" t="s">
         <v>399</v>
       </c>
@@ -24252,7 +24267,7 @@
       <c r="P231" s="15"/>
       <c r="Q231" s="15"/>
     </row>
-    <row r="232" spans="1:17" ht="17.5" thickBot="1">
+    <row r="232" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A232" s="11" t="s">
         <v>399</v>
       </c>
@@ -24295,7 +24310,7 @@
       <c r="P232" s="20"/>
       <c r="Q232" s="20"/>
     </row>
-    <row r="233" spans="1:17" ht="17.5" thickBot="1">
+    <row r="233" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A233" s="11" t="s">
         <v>399</v>
       </c>
@@ -24338,7 +24353,7 @@
       <c r="P233" s="20"/>
       <c r="Q233" s="20"/>
     </row>
-    <row r="234" spans="1:17" ht="17.5" thickBot="1">
+    <row r="234" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A234" s="16" t="s">
         <v>399</v>
       </c>
@@ -24379,7 +24394,7 @@
       <c r="P234" s="15"/>
       <c r="Q234" s="15"/>
     </row>
-    <row r="235" spans="1:17" ht="17.5" thickBot="1">
+    <row r="235" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A235" s="16" t="s">
         <v>399</v>
       </c>
@@ -24422,7 +24437,7 @@
       <c r="P235" s="15"/>
       <c r="Q235" s="15"/>
     </row>
-    <row r="236" spans="1:17" ht="17.5" thickBot="1">
+    <row r="236" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A236" s="16" t="s">
         <v>399</v>
       </c>
@@ -24465,7 +24480,7 @@
       <c r="P236" s="15"/>
       <c r="Q236" s="15"/>
     </row>
-    <row r="237" spans="1:17" ht="17.5" thickBot="1">
+    <row r="237" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A237" s="11" t="s">
         <v>399</v>
       </c>
@@ -24508,7 +24523,7 @@
       <c r="P237" s="15"/>
       <c r="Q237" s="15"/>
     </row>
-    <row r="238" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="238" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A238" s="16" t="s">
         <v>399</v>
       </c>
@@ -24559,7 +24574,7 @@
       </c>
       <c r="Q238" s="19"/>
     </row>
-    <row r="239" spans="1:17" ht="17.5" thickBot="1">
+    <row r="239" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A239" s="16" t="s">
         <v>399</v>
       </c>
@@ -24604,7 +24619,7 @@
       </c>
       <c r="Q239" s="19"/>
     </row>
-    <row r="240" spans="1:17" ht="17.5" thickBot="1">
+    <row r="240" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A240" s="16" t="s">
         <v>399</v>
       </c>
@@ -24655,7 +24670,7 @@
       </c>
       <c r="Q240" s="19"/>
     </row>
-    <row r="241" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="241" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A241" s="16" t="s">
         <v>399</v>
       </c>
@@ -24706,7 +24721,7 @@
       </c>
       <c r="Q241" s="19"/>
     </row>
-    <row r="242" spans="1:17" ht="17.5" thickBot="1">
+    <row r="242" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A242" s="16" t="s">
         <v>399</v>
       </c>
@@ -24757,7 +24772,7 @@
       </c>
       <c r="Q242" s="19"/>
     </row>
-    <row r="243" spans="1:17" ht="17.5" thickBot="1">
+    <row r="243" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A243" s="52" t="s">
         <v>399</v>
       </c>
@@ -24792,7 +24807,7 @@
       <c r="P243" s="60"/>
       <c r="Q243" s="68"/>
     </row>
-    <row r="244" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="244" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A244" s="16" t="s">
         <v>399</v>
       </c>
@@ -24835,7 +24850,7 @@
       <c r="P244" s="19"/>
       <c r="Q244" s="19"/>
     </row>
-    <row r="245" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="245" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A245" s="16" t="s">
         <v>399</v>
       </c>
@@ -24876,7 +24891,7 @@
       <c r="P245" s="19"/>
       <c r="Q245" s="19"/>
     </row>
-    <row r="246" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="246" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A246" s="52" t="s">
         <v>399</v>
       </c>
@@ -24921,7 +24936,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="247" spans="1:17" ht="17.5" thickBot="1">
+    <row r="247" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A247" s="52" t="s">
         <v>399</v>
       </c>
@@ -24962,7 +24977,7 @@
       <c r="P247" s="60"/>
       <c r="Q247" s="60"/>
     </row>
-    <row r="248" spans="1:17" ht="17.5" thickBot="1">
+    <row r="248" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A248" s="52" t="s">
         <v>399</v>
       </c>
@@ -25003,7 +25018,7 @@
       <c r="P248" s="60"/>
       <c r="Q248" s="60"/>
     </row>
-    <row r="249" spans="1:17" ht="17.5" thickBot="1">
+    <row r="249" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A249" s="52" t="s">
         <v>399</v>
       </c>
@@ -25044,7 +25059,7 @@
       <c r="P249" s="60"/>
       <c r="Q249" s="60"/>
     </row>
-    <row r="250" spans="1:17" ht="17.5" thickBot="1">
+    <row r="250" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A250" s="52" t="s">
         <v>399</v>
       </c>
@@ -25085,7 +25100,7 @@
       <c r="P250" s="60"/>
       <c r="Q250" s="60"/>
     </row>
-    <row r="251" spans="1:17" ht="17.5" thickBot="1">
+    <row r="251" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A251" s="52" t="s">
         <v>399</v>
       </c>
@@ -25128,7 +25143,7 @@
       <c r="P251" s="60"/>
       <c r="Q251" s="60"/>
     </row>
-    <row r="252" spans="1:17" ht="17.5" thickBot="1">
+    <row r="252" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A252" s="52" t="s">
         <v>399</v>
       </c>
@@ -25179,7 +25194,7 @@
       </c>
       <c r="Q252" s="68"/>
     </row>
-    <row r="253" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="253" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A253" s="55" t="s">
         <v>399</v>
       </c>
@@ -25222,7 +25237,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="254" spans="1:17" ht="17.5" thickBot="1">
+    <row r="254" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A254" s="55" t="s">
         <v>399</v>
       </c>
@@ -25263,7 +25278,7 @@
       <c r="P254" s="68"/>
       <c r="Q254" s="60"/>
     </row>
-    <row r="255" spans="1:17" ht="17.5" thickBot="1">
+    <row r="255" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A255" s="52" t="s">
         <v>399</v>
       </c>
@@ -25304,7 +25319,7 @@
       <c r="P255" s="68"/>
       <c r="Q255" s="60"/>
     </row>
-    <row r="256" spans="1:17" ht="17.5" thickBot="1">
+    <row r="256" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A256" s="52" t="s">
         <v>399</v>
       </c>
@@ -25345,7 +25360,7 @@
       <c r="P256" s="68"/>
       <c r="Q256" s="60"/>
     </row>
-    <row r="257" spans="1:17" ht="17.5" thickBot="1">
+    <row r="257" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A257" s="52" t="s">
         <v>399</v>
       </c>
@@ -25386,7 +25401,7 @@
       <c r="P257" s="68"/>
       <c r="Q257" s="60"/>
     </row>
-    <row r="258" spans="1:17" ht="17.5" thickBot="1">
+    <row r="258" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A258" s="16" t="s">
         <v>399</v>
       </c>
@@ -25427,7 +25442,7 @@
       <c r="P258" s="15"/>
       <c r="Q258" s="15"/>
     </row>
-    <row r="259" spans="1:17" ht="17.5" thickBot="1">
+    <row r="259" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A259" s="16" t="s">
         <v>399</v>
       </c>
@@ -25470,7 +25485,7 @@
       <c r="P259" s="15"/>
       <c r="Q259" s="15"/>
     </row>
-    <row r="260" spans="1:17" ht="17.5" thickBot="1">
+    <row r="260" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A260" s="16" t="s">
         <v>399</v>
       </c>
@@ -25513,7 +25528,7 @@
       <c r="P260" s="15"/>
       <c r="Q260" s="15"/>
     </row>
-    <row r="261" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="261" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A261" s="16" t="s">
         <v>399</v>
       </c>
@@ -25556,7 +25571,7 @@
       <c r="P261" s="15"/>
       <c r="Q261" s="15"/>
     </row>
-    <row r="262" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="262" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A262" s="11" t="s">
         <v>399</v>
       </c>
@@ -25597,7 +25612,7 @@
       <c r="P262" s="15"/>
       <c r="Q262" s="20"/>
     </row>
-    <row r="263" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="263" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A263" s="97" t="s">
         <v>399</v>
       </c>
@@ -25636,7 +25651,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="264" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="264" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A264" s="11" t="s">
         <v>399</v>
       </c>
@@ -25679,7 +25694,7 @@
       <c r="P264" s="15"/>
       <c r="Q264" s="15"/>
     </row>
-    <row r="265" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="265" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A265" s="11" t="s">
         <v>399</v>
       </c>
@@ -25722,7 +25737,7 @@
       <c r="P265" s="15"/>
       <c r="Q265" s="15"/>
     </row>
-    <row r="266" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="266" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A266" s="11" t="s">
         <v>399</v>
       </c>
@@ -25765,7 +25780,7 @@
       <c r="P266" s="15"/>
       <c r="Q266" s="15"/>
     </row>
-    <row r="267" spans="1:17" ht="17.5" thickBot="1">
+    <row r="267" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A267" s="11" t="s">
         <v>399</v>
       </c>
@@ -25810,7 +25825,7 @@
       <c r="P267" s="15"/>
       <c r="Q267" s="15"/>
     </row>
-    <row r="268" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="268" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A268" s="52" t="s">
         <v>400</v>
       </c>
@@ -25861,7 +25876,7 @@
       </c>
       <c r="Q268" s="68"/>
     </row>
-    <row r="269" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="269" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A269" s="16" t="s">
         <v>400</v>
       </c>
@@ -25902,7 +25917,7 @@
       <c r="P269" s="19"/>
       <c r="Q269" s="19"/>
     </row>
-    <row r="270" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="270" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A270" s="16" t="s">
         <v>400</v>
       </c>
@@ -25941,7 +25956,7 @@
       <c r="P270" s="19"/>
       <c r="Q270" s="19"/>
     </row>
-    <row r="271" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="271" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A271" s="16" t="s">
         <v>400</v>
       </c>
@@ -25982,7 +25997,7 @@
       <c r="P271" s="19"/>
       <c r="Q271" s="19"/>
     </row>
-    <row r="272" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="272" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A272" s="55" t="s">
         <v>400</v>
       </c>
@@ -26033,7 +26048,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="273" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="273" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A273" s="52" t="s">
         <v>400</v>
       </c>
@@ -26072,7 +26087,7 @@
       <c r="P273" s="60"/>
       <c r="Q273" s="60"/>
     </row>
-    <row r="274" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="274" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A274" s="16" t="s">
         <v>400</v>
       </c>
@@ -26113,7 +26128,7 @@
       <c r="P274" s="15"/>
       <c r="Q274" s="15"/>
     </row>
-    <row r="275" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="275" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A275" s="52" t="s">
         <v>400</v>
       </c>
@@ -26166,7 +26181,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="276" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="276" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A276" s="52" t="s">
         <v>400</v>
       </c>
@@ -26217,7 +26232,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="277" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="277" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A277" s="11" t="s">
         <v>400</v>
       </c>
@@ -26260,7 +26275,7 @@
       <c r="P277" s="15"/>
       <c r="Q277" s="15"/>
     </row>
-    <row r="278" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="278" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A278" s="11"/>
       <c r="B278" s="12" t="s">
         <v>1179</v>
@@ -26301,7 +26316,7 @@
       <c r="P278" s="15"/>
       <c r="Q278" s="15"/>
     </row>
-    <row r="279" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="279" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A279" s="16" t="s">
         <v>400</v>
       </c>
@@ -26344,7 +26359,7 @@
       <c r="P279" s="15"/>
       <c r="Q279" s="15"/>
     </row>
-    <row r="280" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="280" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A280" s="55" t="s">
         <v>400</v>
       </c>
@@ -26395,7 +26410,7 @@
       </c>
       <c r="Q280" s="60"/>
     </row>
-    <row r="281" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="281" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A281" s="11" t="s">
         <v>400</v>
       </c>
@@ -26438,7 +26453,7 @@
       <c r="P281" s="15"/>
       <c r="Q281" s="15"/>
     </row>
-    <row r="282" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="282" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A282" s="52" t="s">
         <v>400</v>
       </c>
@@ -26481,7 +26496,7 @@
       <c r="P282" s="68"/>
       <c r="Q282" s="68"/>
     </row>
-    <row r="283" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="283" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A283" s="52" t="s">
         <v>400</v>
       </c>
@@ -26522,7 +26537,7 @@
       <c r="P283" s="68"/>
       <c r="Q283" s="68"/>
     </row>
-    <row r="284" spans="1:17" s="30" customFormat="1" ht="21.5" customHeight="1" thickBot="1">
+    <row r="284" spans="1:17" s="30" customFormat="1" ht="21.5" hidden="1" customHeight="1" thickBot="1">
       <c r="A284" s="16" t="s">
         <v>400</v>
       </c>
@@ -26563,7 +26578,7 @@
       <c r="P284" s="35"/>
       <c r="Q284" s="35"/>
     </row>
-    <row r="285" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="285" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A285" s="16" t="s">
         <v>400</v>
       </c>
@@ -26606,7 +26621,7 @@
       <c r="P285" s="19"/>
       <c r="Q285" s="19"/>
     </row>
-    <row r="286" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="286" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A286" s="52" t="s">
         <v>400</v>
       </c>
@@ -26649,7 +26664,7 @@
       <c r="P286" s="68"/>
       <c r="Q286" s="68"/>
     </row>
-    <row r="287" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="287" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A287" s="16" t="s">
         <v>400</v>
       </c>
@@ -26692,7 +26707,7 @@
       <c r="P287" s="19"/>
       <c r="Q287" s="38"/>
     </row>
-    <row r="288" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="288" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A288" s="16" t="s">
         <v>400</v>
       </c>
@@ -26733,7 +26748,7 @@
       <c r="P288" s="19"/>
       <c r="Q288" s="19"/>
     </row>
-    <row r="289" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="289" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A289" s="16" t="s">
         <v>400</v>
       </c>
@@ -26776,7 +26791,7 @@
       <c r="P289" s="19"/>
       <c r="Q289" s="19"/>
     </row>
-    <row r="290" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="290" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A290" s="50" t="s">
         <v>400</v>
       </c>
@@ -26829,7 +26844,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="291" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="291" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A291" s="16" t="s">
         <v>400</v>
       </c>
@@ -26870,7 +26885,7 @@
       <c r="P291" s="19"/>
       <c r="Q291" s="19"/>
     </row>
-    <row r="292" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="292" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A292" s="11" t="s">
         <v>400</v>
       </c>
@@ -26913,7 +26928,7 @@
       <c r="P292" s="15"/>
       <c r="Q292" s="15"/>
     </row>
-    <row r="293" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="293" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A293" s="11" t="s">
         <v>400</v>
       </c>
@@ -26956,7 +26971,7 @@
       <c r="P293" s="15"/>
       <c r="Q293" s="15"/>
     </row>
-    <row r="294" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="294" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A294" s="16" t="s">
         <v>400</v>
       </c>
@@ -26997,7 +27012,7 @@
       <c r="P294" s="35"/>
       <c r="Q294" s="35"/>
     </row>
-    <row r="295" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="295" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A295" s="16" t="s">
         <v>400</v>
       </c>
@@ -27036,7 +27051,7 @@
       <c r="P295" s="35"/>
       <c r="Q295" s="35"/>
     </row>
-    <row r="296" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="296" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A296" s="11" t="s">
         <v>400</v>
       </c>
@@ -27075,7 +27090,7 @@
       <c r="P296" s="35"/>
       <c r="Q296" s="35"/>
     </row>
-    <row r="297" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="297" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A297" s="108" t="s">
         <v>400</v>
       </c>
@@ -27110,7 +27125,7 @@
       <c r="P297" s="115"/>
       <c r="Q297" s="115"/>
     </row>
-    <row r="298" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="298" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A298" s="52" t="s">
         <v>400</v>
       </c>
@@ -27159,7 +27174,7 @@
       </c>
       <c r="Q298" s="53"/>
     </row>
-    <row r="299" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="299" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A299" s="55" t="s">
         <v>400</v>
       </c>
@@ -27198,7 +27213,7 @@
       <c r="P299" s="60"/>
       <c r="Q299" s="60"/>
     </row>
-    <row r="300" spans="1:17" ht="17.5" thickBot="1">
+    <row r="300" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A300" s="55" t="s">
         <v>400</v>
       </c>
@@ -27245,7 +27260,7 @@
       </c>
       <c r="Q300" s="60"/>
     </row>
-    <row r="301" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="301" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A301" s="55" t="s">
         <v>400</v>
       </c>
@@ -27292,7 +27307,7 @@
       </c>
       <c r="Q301" s="60"/>
     </row>
-    <row r="302" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="302" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A302" s="55" t="s">
         <v>400</v>
       </c>
@@ -27335,7 +27350,7 @@
       <c r="P302" s="68"/>
       <c r="Q302" s="68"/>
     </row>
-    <row r="303" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="303" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A303" s="55" t="s">
         <v>400</v>
       </c>
@@ -27378,7 +27393,7 @@
       <c r="P303" s="60"/>
       <c r="Q303" s="60"/>
     </row>
-    <row r="304" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="304" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A304" s="11" t="s">
         <v>400</v>
       </c>
@@ -27421,7 +27436,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="305" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="305" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A305" s="52" t="s">
         <v>400</v>
       </c>
@@ -27462,7 +27477,7 @@
       <c r="P305" s="68"/>
       <c r="Q305" s="68"/>
     </row>
-    <row r="306" spans="1:17" ht="17.5" thickBot="1">
+    <row r="306" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A306" s="52" t="s">
         <v>400</v>
       </c>
@@ -27509,7 +27524,7 @@
       <c r="P306" s="68"/>
       <c r="Q306" s="68"/>
     </row>
-    <row r="307" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="307" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A307" s="16" t="s">
         <v>400</v>
       </c>
@@ -27558,7 +27573,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="308" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="308" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A308" s="16" t="s">
         <v>400</v>
       </c>
@@ -27601,7 +27616,7 @@
       <c r="P308" s="19"/>
       <c r="Q308" s="19"/>
     </row>
-    <row r="309" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="309" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A309" s="16" t="s">
         <v>400</v>
       </c>
@@ -27642,7 +27657,7 @@
       <c r="P309" s="19"/>
       <c r="Q309" s="35"/>
     </row>
-    <row r="310" spans="1:17" ht="17.5" thickBot="1">
+    <row r="310" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A310" s="11" t="s">
         <v>400</v>
       </c>
@@ -27683,7 +27698,7 @@
       <c r="P310" s="15"/>
       <c r="Q310" s="15"/>
     </row>
-    <row r="311" spans="1:17" ht="17.5" thickBot="1">
+    <row r="311" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A311" s="11" t="s">
         <v>400</v>
       </c>
@@ -27726,7 +27741,7 @@
       <c r="P311" s="20"/>
       <c r="Q311" s="20"/>
     </row>
-    <row r="312" spans="1:17" ht="17" customHeight="1" thickBot="1">
+    <row r="312" spans="1:17" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A312" s="11" t="s">
         <v>400</v>
       </c>
@@ -27767,7 +27782,7 @@
       <c r="P312" s="15"/>
       <c r="Q312" s="15"/>
     </row>
-    <row r="313" spans="1:17" s="30" customFormat="1" ht="17.5" thickBot="1">
+    <row r="313" spans="1:17" s="30" customFormat="1" ht="17.5" hidden="1" thickBot="1">
       <c r="A313" s="11" t="s">
         <v>400</v>
       </c>
@@ -27814,7 +27829,7 @@
       <c r="P313" s="15"/>
       <c r="Q313" s="15"/>
     </row>
-    <row r="314" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="314" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A314" s="55" t="s">
         <v>399</v>
       </c>
@@ -27855,7 +27870,7 @@
       <c r="P314" s="60"/>
       <c r="Q314" s="60"/>
     </row>
-    <row r="315" spans="1:17" s="30" customFormat="1" ht="17" customHeight="1" thickBot="1">
+    <row r="315" spans="1:17" s="30" customFormat="1" ht="17" hidden="1" customHeight="1" thickBot="1">
       <c r="A315" s="11" t="s">
         <v>399</v>
       </c>
@@ -27894,7 +27909,7 @@
       <c r="P315" s="15"/>
       <c r="Q315" s="15"/>
     </row>
-    <row r="316" spans="1:17" ht="17.5" thickBot="1">
+    <row r="316" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A316" s="11" t="s">
         <v>399</v>
       </c>
@@ -27933,7 +27948,7 @@
       <c r="P316" s="15"/>
       <c r="Q316" s="15"/>
     </row>
-    <row r="317" spans="1:17" ht="17.5" thickBot="1">
+    <row r="317" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A317" s="97" t="s">
         <v>399</v>
       </c>
@@ -27976,7 +27991,7 @@
       <c r="P317" s="16"/>
       <c r="Q317" s="16"/>
     </row>
-    <row r="318" spans="1:17" ht="17.5" thickBot="1">
+    <row r="318" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A318" s="11" t="s">
         <v>824</v>
       </c>
@@ -28027,7 +28042,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="319" spans="1:17" ht="17.5" thickBot="1">
+    <row r="319" spans="1:17" ht="17.5" hidden="1" thickBot="1">
       <c r="A319" s="11" t="s">
         <v>399</v>
       </c>
@@ -28073,157 +28088,171 @@
       <c r="Q319" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q317" xr:uid="{B32A8820-8DD9-4523-92F1-AE1BB6EB06C7}"/>
-  <conditionalFormatting sqref="A143:J143 A32:J32 A48:J48 A50:J52 A63:J63 A65:J65 A71:J71 A82:J82 A84:J85 A112:J115 A118:J119 A122:J122 A124:J125 A180:J180 A212:J212 A228:J228 A260:J261 A270:J270 A272:J273 A283:J283 A59:J59 A171:J171 A49:L49 A19:N20 A31:L31 A61:L62 A83:L83 A120:N121 A123:L123 A271:K271 A298:L298 A169:N170 A276:J281 A230:J231 A282:L282 A183:J184 A168:J168 A60:E60 G60:J60 A254:L254 A255:J257 K138:N138 K59:N60 A13:N13 A15:N15 A64:N64 A68:N70 A116:N117 K277:N281 A53:N58 A259:N259 A130:N131 K135 A139:N141 A142:L142 N142 A144:N163 A185:N211 A229:N229 A33:N36 A126:K126 K118:N118 A252:N253 N271 A274:N274 A275:K275 N275 N282 A269:L269 N269 N126 N135:N137 A294:K294 N294 N298 A284:N293 A38:N38 A2:M2 A72:N81 A132:J132 A303:N308 A11:I12 A7:J10 M65 A134:J138 A166:N167 I319 A232:N238 M319:N319 A213:N217 A40:N47 K11 A220:N224 A219:I219 M219:N219 A67:J67 A239:J239 A25:N30 K22:N23 A21:J23 A262:N268 A127:J129 A86:N107 A109:N111 A108:H108 J108:N108 A226:N227 L255:L257 A247:J251 K219 A37:K37 N37 A164:J165 A240:N246 A299:J302 A295:J297 A16:J18 A181:N182 A172:N179 A3:N6 A310:N316">
-    <cfRule type="expression" dxfId="243" priority="243">
+  <autoFilter ref="A1:Q319" xr:uid="{B32A8820-8DD9-4523-92F1-AE1BB6EB06C7}">
+    <filterColumn colId="9">
+      <filters>
+        <dateGroupItem year="2569" month="8" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A143:J143 A32:J32 A48:J48 A50:J52 A63:J63 A65:J65 A71:J71 A82:J82 A84:J85 A112:J115 A118:J119 A122:J122 A124:J125 A180:J180 A228:J228 A260:J261 A270:J270 A272:J273 A283:J283 A59:J59 A171:J171 A49:L49 A19:N20 A31:L31 A61:L62 A83:L83 A120:N121 A123:L123 A271:K271 A298:L298 A169:N170 A276:J281 A230:J231 A282:L282 A183:J184 A168:J168 A60:E60 G60:J60 A254:L254 A255:J257 K138:N138 K59:N60 A13:N13 A15:N15 A64:N64 A68:N70 A116:N117 K277:N281 A53:N58 A259:N259 A130:N131 K135 A139:N141 A142:L142 N142 A144:N163 A185:N211 A229:N229 A33:N36 A126:K126 K118:N118 A252:N253 N271 A274:N274 A275:K275 N275 N282 A269:L269 N269 N126 N135:N137 A294:K294 N294 N298 A284:N293 A38:N38 A2:M2 A72:N81 A132:J132 A303:N308 A11:I12 A7:J10 M65 A134:J138 A166:N167 I319 A232:N238 M319:N319 A213:N217 A40:N47 K11 A220:N224 A219:I219 M219:N219 A67:J67 A239:J239 A25:N30 K22:N23 A21:J23 A262:N268 A127:J129 A86:N107 A109:N111 A108:H108 J108:N108 A226:N227 L255:L257 A247:J251 K219 A37:K37 N37 A164:J165 A240:N246 A299:J302 A295:J297 A16:J18 A181:N182 A172:N179 A3:N6 A310:N316 A212:J212">
+    <cfRule type="expression" dxfId="245" priority="245">
       <formula>$W2=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="242" priority="244">
+    <cfRule type="expression" dxfId="244" priority="246">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A319">
-    <cfRule type="expression" dxfId="241" priority="241">
+    <cfRule type="expression" dxfId="243" priority="243">
       <formula>$W319=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="240" priority="242">
+    <cfRule type="expression" dxfId="242" priority="244">
       <formula>$W319=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="expression" dxfId="239" priority="240">
+    <cfRule type="expression" dxfId="241" priority="242">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11">
-    <cfRule type="expression" dxfId="238" priority="238">
+    <cfRule type="expression" dxfId="240" priority="240">
       <formula>$W11=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="237" priority="239">
+    <cfRule type="expression" dxfId="239" priority="241">
       <formula>$W11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M31">
-    <cfRule type="expression" dxfId="236" priority="236">
+    <cfRule type="expression" dxfId="238" priority="238">
       <formula>$W31=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="235" priority="237">
+    <cfRule type="expression" dxfId="237" priority="239">
       <formula>$W31=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M254:N254 M255:M257">
-    <cfRule type="expression" dxfId="234" priority="234">
+    <cfRule type="expression" dxfId="236" priority="236">
       <formula>$W254=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="233" priority="235">
+    <cfRule type="expression" dxfId="235" priority="237">
       <formula>$W254=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:N14">
-    <cfRule type="expression" dxfId="232" priority="232">
+    <cfRule type="expression" dxfId="234" priority="234">
       <formula>$W14=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="231" priority="233">
+    <cfRule type="expression" dxfId="233" priority="235">
       <formula>$W14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M49:N49">
-    <cfRule type="expression" dxfId="230" priority="230">
+    <cfRule type="expression" dxfId="232" priority="232">
       <formula>$W49=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="229" priority="231">
+    <cfRule type="expression" dxfId="231" priority="233">
       <formula>$W49=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M61:N62">
-    <cfRule type="expression" dxfId="228" priority="228">
+    <cfRule type="expression" dxfId="230" priority="230">
       <formula>$W61=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="227" priority="229">
+    <cfRule type="expression" dxfId="229" priority="231">
       <formula>$W61=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M67:N67">
-    <cfRule type="expression" dxfId="226" priority="226">
+    <cfRule type="expression" dxfId="228" priority="228">
       <formula>$W67=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="225" priority="227">
+    <cfRule type="expression" dxfId="227" priority="229">
       <formula>$W67=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83:N83">
-    <cfRule type="expression" dxfId="224" priority="224">
+    <cfRule type="expression" dxfId="226" priority="226">
       <formula>$W83=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="223" priority="225">
+    <cfRule type="expression" dxfId="225" priority="227">
       <formula>$W83=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M123:N123">
-    <cfRule type="expression" dxfId="222" priority="222">
+    <cfRule type="expression" dxfId="224" priority="224">
       <formula>$W123=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="221" priority="223">
+    <cfRule type="expression" dxfId="223" priority="225">
       <formula>$W123=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31">
-    <cfRule type="expression" dxfId="220" priority="220">
+    <cfRule type="expression" dxfId="222" priority="222">
       <formula>$W31=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="219" priority="221">
+    <cfRule type="expression" dxfId="221" priority="223">
       <formula>$W31=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112">
-    <cfRule type="expression" dxfId="218" priority="218">
+    <cfRule type="expression" dxfId="220" priority="220">
       <formula>$W112=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="217" priority="218">
+    <cfRule type="expression" dxfId="219" priority="220">
       <formula>$W112=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N65">
-    <cfRule type="expression" dxfId="216" priority="219">
+    <cfRule type="expression" dxfId="218" priority="221">
       <formula>$W65=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="215" priority="245">
+    <cfRule type="expression" dxfId="217" priority="247">
       <formula>$W65=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M142">
-    <cfRule type="expression" dxfId="214" priority="216">
+    <cfRule type="expression" dxfId="216" priority="218">
       <formula>$W142=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="213" priority="217">
+    <cfRule type="expression" dxfId="215" priority="219">
       <formula>$W142=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M112">
-    <cfRule type="expression" dxfId="212" priority="212">
+    <cfRule type="expression" dxfId="214" priority="214">
       <formula>$W112=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="213">
+    <cfRule type="expression" dxfId="213" priority="215">
       <formula>$W112=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M135:M137">
-    <cfRule type="expression" dxfId="210" priority="210">
+    <cfRule type="expression" dxfId="212" priority="212">
       <formula>$W135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="210">
+    <cfRule type="expression" dxfId="211" priority="212">
       <formula>$W135=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L271:M271">
-    <cfRule type="expression" dxfId="208" priority="211">
+    <cfRule type="expression" dxfId="210" priority="213">
       <formula>$W271=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="207" priority="246">
+    <cfRule type="expression" dxfId="209" priority="248">
       <formula>$W271=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L275">
+    <cfRule type="expression" dxfId="208" priority="210">
+      <formula>$W275=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="207" priority="211">
+      <formula>$W275=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M275">
     <cfRule type="expression" dxfId="206" priority="208">
       <formula>$W275=2</formula>
     </cfRule>
@@ -28231,200 +28260,200 @@
       <formula>$W275=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M275">
+  <conditionalFormatting sqref="M282">
     <cfRule type="expression" dxfId="204" priority="206">
-      <formula>$W275=2</formula>
+      <formula>$W282=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="203" priority="207">
-      <formula>$W275=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M282">
-    <cfRule type="expression" dxfId="202" priority="204">
-      <formula>$W282=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="201" priority="205">
       <formula>$W282=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M269">
-    <cfRule type="expression" dxfId="200" priority="202">
+    <cfRule type="expression" dxfId="202" priority="204">
       <formula>$W269=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="199" priority="203">
+    <cfRule type="expression" dxfId="201" priority="205">
       <formula>$W269=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M113:M115">
-    <cfRule type="expression" dxfId="198" priority="198">
+    <cfRule type="expression" dxfId="200" priority="200">
       <formula>$W113=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="199">
+    <cfRule type="expression" dxfId="199" priority="201">
       <formula>$W113=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L113:L115">
-    <cfRule type="expression" dxfId="196" priority="200">
+    <cfRule type="expression" dxfId="198" priority="202">
       <formula>$W113=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="201">
+    <cfRule type="expression" dxfId="197" priority="203">
       <formula>$W113=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M126:M129">
-    <cfRule type="expression" dxfId="194" priority="194">
+    <cfRule type="expression" dxfId="196" priority="196">
       <formula>$W126=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="195">
+    <cfRule type="expression" dxfId="195" priority="197">
       <formula>$W126=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L126:L129">
-    <cfRule type="expression" dxfId="192" priority="196">
+    <cfRule type="expression" dxfId="194" priority="198">
       <formula>$W126=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="197">
+    <cfRule type="expression" dxfId="193" priority="199">
       <formula>$W126=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L135:L137">
-    <cfRule type="expression" dxfId="190" priority="192">
+    <cfRule type="expression" dxfId="192" priority="194">
       <formula>$W135=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="193">
+    <cfRule type="expression" dxfId="191" priority="195">
       <formula>$W135=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M294">
-    <cfRule type="expression" dxfId="188" priority="188">
+    <cfRule type="expression" dxfId="190" priority="190">
       <formula>$W294=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="187" priority="188">
+    <cfRule type="expression" dxfId="189" priority="190">
       <formula>$W294=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L294">
-    <cfRule type="expression" dxfId="186" priority="189">
+    <cfRule type="expression" dxfId="188" priority="191">
       <formula>$W294=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="247">
+    <cfRule type="expression" dxfId="187" priority="249">
       <formula>$W294=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M295:M297">
-    <cfRule type="expression" dxfId="184" priority="184">
+    <cfRule type="expression" dxfId="186" priority="186">
       <formula>$W295=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="184">
+    <cfRule type="expression" dxfId="185" priority="186">
       <formula>$W295=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L295:L297">
-    <cfRule type="expression" dxfId="182" priority="185">
+    <cfRule type="expression" dxfId="184" priority="187">
       <formula>$W295=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="248">
+    <cfRule type="expression" dxfId="183" priority="250">
       <formula>$W295=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M298">
-    <cfRule type="expression" dxfId="180" priority="180">
+    <cfRule type="expression" dxfId="182" priority="182">
       <formula>$W298=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="181">
+    <cfRule type="expression" dxfId="181" priority="183">
       <formula>$W298=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
-    <cfRule type="expression" dxfId="178" priority="178">
+    <cfRule type="expression" dxfId="180" priority="180">
       <formula>$W2=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="179">
+    <cfRule type="expression" dxfId="179" priority="181">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A133:N133">
-    <cfRule type="expression" dxfId="176" priority="176">
+    <cfRule type="expression" dxfId="178" priority="178">
       <formula>$W133=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="177">
+    <cfRule type="expression" dxfId="177" priority="179">
       <formula>$W133=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:H24 L24:N24">
-    <cfRule type="expression" dxfId="174" priority="174">
+    <cfRule type="expression" dxfId="176" priority="176">
       <formula>$W24=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="175">
+    <cfRule type="expression" dxfId="175" priority="177">
       <formula>$W24=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="expression" dxfId="172" priority="172">
+    <cfRule type="expression" dxfId="174" priority="174">
       <formula>$W32=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="173">
+    <cfRule type="expression" dxfId="173" priority="175">
       <formula>$W32=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11">
-    <cfRule type="expression" dxfId="170" priority="170">
+    <cfRule type="expression" dxfId="172" priority="172">
       <formula>$W11=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="170">
+    <cfRule type="expression" dxfId="171" priority="172">
       <formula>$W11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A258:I258 K258:N258">
-    <cfRule type="expression" dxfId="168" priority="171">
+    <cfRule type="expression" dxfId="170" priority="173">
       <formula>$W258=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="167" priority="249">
+    <cfRule type="expression" dxfId="169" priority="251">
       <formula>$W258=2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N261">
-    <cfRule type="expression" dxfId="166" priority="168">
+    <cfRule type="expression" dxfId="168" priority="170">
       <formula>$W261=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="169">
+    <cfRule type="expression" dxfId="167" priority="171">
       <formula>$W261=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N260">
-    <cfRule type="expression" dxfId="164" priority="166">
+    <cfRule type="expression" dxfId="166" priority="168">
       <formula>$W260=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="163" priority="167">
+    <cfRule type="expression" dxfId="165" priority="169">
       <formula>$W260=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11">
-    <cfRule type="expression" dxfId="162" priority="162">
+    <cfRule type="expression" dxfId="164" priority="164">
       <formula>$W11=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="163">
+    <cfRule type="expression" dxfId="163" priority="165">
       <formula>$W11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O319 O264:O266 O40:O65 O226:O257 O219:O223 O166:O217 O67:O162 O310:O316 O2:O38 O268:O308">
-    <cfRule type="cellIs" dxfId="160" priority="157" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="159" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="158" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="160" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="159" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="161" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="160" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="162" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="161" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="163" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M318:N318 I318:J318">
+    <cfRule type="expression" dxfId="157" priority="157">
+      <formula>$W318=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="156" priority="158">
+      <formula>$W318=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A318">
     <cfRule type="expression" dxfId="155" priority="155">
       <formula>$W318=2</formula>
     </cfRule>
@@ -28432,37 +28461,37 @@
       <formula>$W318=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A318">
-    <cfRule type="expression" dxfId="153" priority="153">
-      <formula>$W318=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="154">
-      <formula>$W318=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B318">
-    <cfRule type="expression" dxfId="151" priority="152">
+    <cfRule type="expression" dxfId="153" priority="154">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O318">
-    <cfRule type="cellIs" dxfId="150" priority="147" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="149" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="148" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="150" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="151" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="150" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="152" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="151" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="153" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I317:N317">
+    <cfRule type="expression" dxfId="147" priority="147">
+      <formula>$W317=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="148">
+      <formula>$W317=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A317">
     <cfRule type="expression" dxfId="145" priority="145">
       <formula>$W317=2</formula>
     </cfRule>
@@ -28470,61 +28499,61 @@
       <formula>$W317=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A317">
-    <cfRule type="expression" dxfId="143" priority="143">
-      <formula>$W317=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="144">
-      <formula>$W317=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B317">
-    <cfRule type="expression" dxfId="141" priority="142">
+    <cfRule type="expression" dxfId="143" priority="144">
       <formula>#REF!&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O317">
-    <cfRule type="cellIs" dxfId="140" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="139" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="140" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="139" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="141" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="142" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="141" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="143" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L318">
-    <cfRule type="expression" dxfId="135" priority="135">
+    <cfRule type="expression" dxfId="137" priority="137">
       <formula>$W318=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="136">
+    <cfRule type="expression" dxfId="136" priority="138">
       <formula>$W318=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L319">
-    <cfRule type="expression" dxfId="133" priority="133">
+    <cfRule type="expression" dxfId="135" priority="135">
       <formula>$W319=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="134">
+    <cfRule type="expression" dxfId="134" priority="136">
       <formula>$W319=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K318">
-    <cfRule type="expression" dxfId="131" priority="131">
+    <cfRule type="expression" dxfId="133" priority="133">
       <formula>$W318=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="132">
+    <cfRule type="expression" dxfId="132" priority="134">
       <formula>$W318=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K319">
+    <cfRule type="expression" dxfId="131" priority="131">
+      <formula>$W319=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="132">
+      <formula>$W319=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J319">
     <cfRule type="expression" dxfId="129" priority="129">
       <formula>$W319=2</formula>
     </cfRule>
@@ -28532,81 +28561,81 @@
       <formula>$W319=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J319">
+  <conditionalFormatting sqref="N12">
     <cfRule type="expression" dxfId="127" priority="127">
-      <formula>$W319=2</formula>
+      <formula>$W12=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="126" priority="128">
-      <formula>$W319=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N12">
-    <cfRule type="expression" dxfId="125" priority="125">
-      <formula>$W12=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="126">
       <formula>$W12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:J39 L39:N39">
-    <cfRule type="expression" dxfId="123" priority="123">
+    <cfRule type="expression" dxfId="125" priority="125">
       <formula>$W39=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="124">
+    <cfRule type="expression" dxfId="124" priority="126">
       <formula>$W39=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O39">
-    <cfRule type="cellIs" dxfId="121" priority="118" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="120" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="119" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="121" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="120" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="122" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="121" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="123" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="124" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="expression" dxfId="116" priority="116">
+    <cfRule type="expression" dxfId="118" priority="118">
       <formula>$W39=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="115" priority="117">
+    <cfRule type="expression" dxfId="117" priority="119">
       <formula>$W39=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A309:H309 M309:N309">
-    <cfRule type="expression" dxfId="114" priority="114">
+    <cfRule type="expression" dxfId="116" priority="116">
       <formula>$W309=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="115">
+    <cfRule type="expression" dxfId="115" priority="117">
       <formula>$W309=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O309">
-    <cfRule type="cellIs" dxfId="112" priority="109" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="111" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="110" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="112" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="111" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="113" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="112" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="114" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="115" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I309">
+    <cfRule type="expression" dxfId="109" priority="109">
+      <formula>$W309=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="110">
+      <formula>$W309=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J309">
     <cfRule type="expression" dxfId="107" priority="107">
       <formula>$W309=2</formula>
     </cfRule>
@@ -28614,106 +28643,106 @@
       <formula>$W309=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J309">
+  <conditionalFormatting sqref="J11">
     <cfRule type="expression" dxfId="105" priority="105">
-      <formula>$W309=2</formula>
+      <formula>$W11=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="104" priority="106">
-      <formula>$W309=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="expression" dxfId="103" priority="103">
-      <formula>$W11=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="104">
       <formula>$W11=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="expression" dxfId="101" priority="101">
+    <cfRule type="expression" dxfId="103" priority="103">
       <formula>$W12=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="102">
+    <cfRule type="expression" dxfId="102" priority="104">
       <formula>$W12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N129">
-    <cfRule type="expression" dxfId="99" priority="99">
+    <cfRule type="expression" dxfId="101" priority="101">
       <formula>$W129=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="100">
+    <cfRule type="expression" dxfId="100" priority="102">
       <formula>$W129=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O259">
-    <cfRule type="cellIs" dxfId="97" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="96" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="97" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="98" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="99" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="100" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O260">
-    <cfRule type="cellIs" dxfId="92" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="91" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="92" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="91" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="93" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="94" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="95" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O261">
-    <cfRule type="cellIs" dxfId="87" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="86" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="87" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="88" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="89" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="90" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A218:N218">
-    <cfRule type="expression" dxfId="82" priority="82">
+    <cfRule type="expression" dxfId="84" priority="84">
       <formula>$W218=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="83">
+    <cfRule type="expression" dxfId="83" priority="85">
       <formula>$W218=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L219">
-    <cfRule type="expression" dxfId="80" priority="80">
+    <cfRule type="expression" dxfId="82" priority="82">
       <formula>$W219=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="81">
+    <cfRule type="expression" dxfId="81" priority="83">
       <formula>$W219=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66:J66">
+    <cfRule type="expression" dxfId="80" priority="80">
+      <formula>$W66=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="81">
+      <formula>$W66=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M66:N66">
     <cfRule type="expression" dxfId="78" priority="78">
       <formula>$W66=2</formula>
     </cfRule>
@@ -28721,32 +28750,32 @@
       <formula>$W66=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M66:N66">
-    <cfRule type="expression" dxfId="76" priority="76">
-      <formula>$W66=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="77">
-      <formula>$W66=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="O66">
-    <cfRule type="cellIs" dxfId="74" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="73" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="74" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="73" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="75" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="76" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="77" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
+    <cfRule type="expression" dxfId="71" priority="71">
+      <formula>$W24=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="72">
+      <formula>$W24=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24">
     <cfRule type="expression" dxfId="69" priority="69">
       <formula>$W24=2</formula>
     </cfRule>
@@ -28754,184 +28783,184 @@
       <formula>$W24=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24">
+  <conditionalFormatting sqref="K129">
     <cfRule type="expression" dxfId="67" priority="67">
-      <formula>$W24=2</formula>
+      <formula>$W129=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="66" priority="68">
-      <formula>$W24=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K129">
-    <cfRule type="expression" dxfId="65" priority="65">
-      <formula>$W129=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="66">
       <formula>$W129=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O218">
-    <cfRule type="cellIs" dxfId="63" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="62" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="63" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="64" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="65" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="66" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O163">
-    <cfRule type="cellIs" dxfId="58" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="57" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="58" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="59" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="60" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="61" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O224">
-    <cfRule type="cellIs" dxfId="53" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="52" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="53" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="54" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="55" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="56" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O267">
-    <cfRule type="cellIs" dxfId="48" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="47" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="48" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="49" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="50" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="51" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O263">
-    <cfRule type="cellIs" dxfId="43" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="42" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="43" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="44" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="45" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="46" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O164">
-    <cfRule type="cellIs" dxfId="38" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="37" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="38" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="39" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="40" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="41" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O165">
-    <cfRule type="cellIs" dxfId="33" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="32" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="33" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="34" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="35" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="36" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O258">
-    <cfRule type="cellIs" dxfId="28" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="27" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="31" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O262">
-    <cfRule type="cellIs" dxfId="23" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="22" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="23" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="24" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="25" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="26" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J258">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$W258=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>$W258=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K309">
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>$W309=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="19">
+      <formula>$W309=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L309">
     <cfRule type="expression" dxfId="16" priority="16">
       <formula>$W309=2</formula>
     </cfRule>
@@ -28939,61 +28968,61 @@
       <formula>$W309=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L309">
+  <conditionalFormatting sqref="A225:N225">
     <cfRule type="expression" dxfId="14" priority="14">
-      <formula>$W309=2</formula>
+      <formula>$W225=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="15">
-      <formula>$W309=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A225:N225">
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>$W225=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="13">
       <formula>$W225=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O225">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>"ขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"รอร่างขออนุมัติ"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"ส่งร่างให้พิจารณา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"เจรจา"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
       <formula>"อนุมัติแล้ว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$W24=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>$W24=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J219">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$W219=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$W219=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L37:M37">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$W37=2</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>$W37=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K212">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$W212=2</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$W37=1</formula>
+      <formula>$W212=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
